--- a/resources/mpn.xlsx
+++ b/resources/mpn.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="blank" sheetId="1" state="visible" r:id="rId3"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="61">
   <si>
     <t xml:space="preserve">TITLE</t>
   </si>
@@ -424,7 +424,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -521,15 +521,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5398,7 +5390,6 @@
       <c r="U12" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB12" s="24"/>
       <c r="AS12" s="2" t="n">
         <v>2</v>
       </c>
@@ -5407,7 +5398,6 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB13" s="24"/>
       <c r="AQ13" s="2" t="n">
         <v>1</v>
       </c>
@@ -5419,7 +5409,6 @@
       <c r="U14" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB14" s="24"/>
       <c r="AS14" s="2" t="n">
         <v>2</v>
       </c>
@@ -5432,7 +5421,6 @@
         <v>3</v>
       </c>
       <c r="P15" s="16"/>
-      <c r="AB15" s="24"/>
       <c r="AP15" s="3" t="n">
         <v>1</v>
       </c>
@@ -5444,7 +5432,6 @@
       <c r="U16" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB16" s="24"/>
       <c r="AS16" s="2" t="n">
         <v>2</v>
       </c>
@@ -5453,7 +5440,6 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB17" s="24"/>
       <c r="AP17" s="3" t="n">
         <v>1</v>
       </c>
@@ -5465,7 +5451,6 @@
       <c r="U18" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB18" s="24"/>
       <c r="AS18" s="2" t="n">
         <v>2</v>
       </c>
@@ -5505,7 +5490,7 @@
       <c r="Y19" s="19"/>
       <c r="Z19" s="18"/>
       <c r="AA19" s="19"/>
-      <c r="AB19" s="25"/>
+      <c r="AB19" s="20"/>
       <c r="AC19" s="18"/>
       <c r="AD19" s="19"/>
       <c r="AE19" s="18"/>
@@ -5541,14 +5526,12 @@
       <c r="W20" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB20" s="24"/>
       <c r="AS20" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="W21" s="2"/>
-      <c r="AB21" s="24"/>
       <c r="AP21" s="3" t="n">
         <v>1</v>
       </c>
@@ -5561,7 +5544,6 @@
       <c r="W22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB22" s="24"/>
       <c r="AS22" s="2" t="n">
         <v>2</v>
       </c>
@@ -5571,7 +5553,6 @@
         <v>3</v>
       </c>
       <c r="U23" s="15"/>
-      <c r="AB23" s="24"/>
       <c r="AN23" s="4" t="n">
         <v>1</v>
       </c>
@@ -5580,20 +5561,17 @@
       <c r="W24" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB24" s="24"/>
       <c r="AS24" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="W25" s="15"/>
-      <c r="AB25" s="24"/>
       <c r="AY25" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB26" s="24"/>
       <c r="AN26" s="4" t="n">
         <v>1</v>
       </c>
@@ -5605,7 +5583,6 @@
       <c r="W27" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB27" s="24"/>
       <c r="AS27" s="2" t="n">
         <v>2</v>
       </c>
@@ -5645,7 +5622,7 @@
       <c r="Y28" s="19"/>
       <c r="Z28" s="18"/>
       <c r="AA28" s="19"/>
-      <c r="AB28" s="25"/>
+      <c r="AB28" s="20"/>
       <c r="AC28" s="18"/>
       <c r="AD28" s="19"/>
       <c r="AE28" s="18"/>
@@ -5677,20 +5654,17 @@
       <c r="W29" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB29" s="24"/>
       <c r="AS29" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="W30" s="15"/>
-      <c r="AB30" s="24"/>
       <c r="AY30" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB31" s="24"/>
       <c r="AM31" s="3" t="n">
         <v>1</v>
       </c>
@@ -5702,7 +5676,6 @@
       <c r="W32" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB32" s="24"/>
       <c r="AS32" s="2" t="n">
         <v>2</v>
       </c>
@@ -5717,7 +5690,6 @@
       <c r="Z33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB33" s="24"/>
       <c r="AF33" s="3" t="n">
         <v>2</v>
       </c>
@@ -5729,7 +5701,7 @@
       <c r="W34" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB34" s="24" t="n">
+      <c r="AB34" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5737,13 +5709,12 @@
       <c r="Z35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="W36" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AB36" s="24" t="n">
+      <c r="AB36" s="4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6443,7 +6414,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CK50"/>
+  <dimension ref="A1:CK39"/>
   <sheetFormatPr defaultColWidth="8.76171875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.36"/>
@@ -6973,7 +6944,6 @@
       <c r="Z15" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="AB15" s="24"/>
       <c r="AP15" s="3" t="n">
         <v>1</v>
       </c>
@@ -6983,7 +6953,6 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U16" s="15"/>
-      <c r="AB16" s="24"/>
       <c r="AG16" s="15" t="n">
         <v>1</v>
       </c>
@@ -6995,7 +6964,6 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB17" s="24"/>
       <c r="AP17" s="3" t="n">
         <v>1</v>
       </c>
@@ -7005,7 +6973,6 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U18" s="15"/>
-      <c r="AB18" s="24"/>
       <c r="AG18" s="15" t="n">
         <v>1</v>
       </c>
@@ -7034,7 +7001,7 @@
       <c r="M19" s="19"/>
       <c r="N19" s="23"/>
       <c r="O19" s="19"/>
-      <c r="P19" s="25"/>
+      <c r="P19" s="20"/>
       <c r="Q19" s="18"/>
       <c r="R19" s="19"/>
       <c r="S19" s="18"/>
@@ -7048,7 +7015,7 @@
       </c>
       <c r="Z19" s="18"/>
       <c r="AA19" s="19"/>
-      <c r="AB19" s="25"/>
+      <c r="AB19" s="20"/>
       <c r="AC19" s="18"/>
       <c r="AD19" s="19"/>
       <c r="AE19" s="18"/>
@@ -7083,8 +7050,6 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P20" s="24"/>
-      <c r="AB20" s="24"/>
       <c r="AK20" s="15" t="n">
         <v>1</v>
       </c>
@@ -7096,8 +7061,6 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P21" s="24"/>
-      <c r="AB21" s="24"/>
       <c r="AU21" s="3" t="n">
         <v>1</v>
       </c>
@@ -7109,8 +7072,6 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P22" s="24"/>
-      <c r="AB22" s="24"/>
       <c r="AK22" s="15" t="n">
         <v>1</v>
       </c>
@@ -7125,8 +7086,6 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P23" s="24"/>
-      <c r="AB23" s="24"/>
       <c r="AD23" s="15" t="n">
         <v>3</v>
       </c>
@@ -7138,8 +7097,6 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P24" s="24"/>
-      <c r="AB24" s="24"/>
       <c r="AK24" s="15" t="n">
         <v>1</v>
       </c>
@@ -7151,8 +7108,6 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P25" s="24"/>
-      <c r="AB25" s="24"/>
       <c r="AS25" s="2" t="n">
         <v>1</v>
       </c>
@@ -7161,8 +7116,6 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P26" s="24"/>
-      <c r="AB26" s="24"/>
       <c r="AK26" s="15" t="n">
         <v>1</v>
       </c>
@@ -7203,7 +7156,7 @@
       <c r="Y27" s="19"/>
       <c r="Z27" s="18"/>
       <c r="AA27" s="19"/>
-      <c r="AB27" s="25"/>
+      <c r="AB27" s="20"/>
       <c r="AC27" s="18"/>
       <c r="AD27" s="23" t="n">
         <v>5</v>
@@ -7245,7 +7198,6 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB28" s="24"/>
       <c r="AD28" s="15" t="n">
         <v>5</v>
       </c>
@@ -7269,7 +7221,6 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB29" s="24"/>
       <c r="AD29" s="15" t="n">
         <v>5</v>
       </c>
@@ -7293,7 +7244,6 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB30" s="24"/>
       <c r="AD30" s="15" t="n">
         <v>5</v>
       </c>
@@ -7318,7 +7268,6 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P31" s="16"/>
-      <c r="AB31" s="24"/>
       <c r="AC31" s="15" t="n">
         <v>5</v>
       </c>
@@ -7342,7 +7291,6 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB32" s="24"/>
       <c r="AC32" s="15" t="n">
         <v>5</v>
       </c>
@@ -7366,7 +7314,6 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB33" s="24"/>
       <c r="AC33" s="15" t="n">
         <v>5</v>
       </c>
@@ -7390,7 +7337,6 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB34" s="24"/>
       <c r="AC34" s="15" t="n">
         <v>5</v>
       </c>
@@ -7431,39 +7377,31 @@
       <c r="M35" s="19"/>
       <c r="N35" s="18"/>
       <c r="O35" s="19"/>
-      <c r="P35" s="20"/>
+      <c r="P35" s="22"/>
       <c r="Q35" s="18"/>
       <c r="R35" s="19"/>
       <c r="S35" s="18"/>
       <c r="T35" s="19"/>
-      <c r="U35" s="23"/>
+      <c r="U35" s="18"/>
       <c r="V35" s="18"/>
       <c r="W35" s="19"/>
       <c r="X35" s="18"/>
       <c r="Y35" s="19"/>
       <c r="Z35" s="18"/>
       <c r="AA35" s="19"/>
-      <c r="AB35" s="22" t="n">
-        <v>5</v>
-      </c>
+      <c r="AB35" s="20"/>
       <c r="AC35" s="18"/>
       <c r="AD35" s="19"/>
       <c r="AE35" s="18"/>
       <c r="AF35" s="19"/>
-      <c r="AG35" s="23" t="n">
-        <v>3</v>
-      </c>
+      <c r="AG35" s="18"/>
       <c r="AH35" s="18"/>
-      <c r="AI35" s="23" t="n">
-        <v>2</v>
-      </c>
+      <c r="AI35" s="19"/>
       <c r="AJ35" s="18"/>
       <c r="AK35" s="19"/>
       <c r="AL35" s="18"/>
       <c r="AM35" s="19"/>
-      <c r="AN35" s="23" t="n">
-        <v>1</v>
-      </c>
+      <c r="AN35" s="20"/>
       <c r="AO35" s="18"/>
       <c r="AP35" s="19"/>
       <c r="AQ35" s="18"/>
@@ -7472,127 +7410,13 @@
       <c r="AT35" s="18"/>
       <c r="AU35" s="19"/>
       <c r="AV35" s="18"/>
-      <c r="AW35" s="19" t="n">
-        <v>1</v>
-      </c>
+      <c r="AW35" s="19"/>
       <c r="AX35" s="18"/>
       <c r="AY35" s="19"/>
       <c r="AZ35" s="20"/>
-      <c r="BE35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI35" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB36" s="24"/>
-      <c r="AZ36" s="4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB37" s="24"/>
-      <c r="AW37" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB38" s="24"/>
-      <c r="AZ38" s="4" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P39" s="16"/>
-      <c r="AB39" s="24"/>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB40" s="24"/>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB41" s="24"/>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB42" s="24"/>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="22"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="19"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="19"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="18"/>
-      <c r="W43" s="19"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="19"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="19"/>
-      <c r="AB43" s="25"/>
-      <c r="AC43" s="18"/>
-      <c r="AD43" s="19"/>
-      <c r="AE43" s="18"/>
-      <c r="AF43" s="19"/>
-      <c r="AG43" s="18"/>
-      <c r="AH43" s="18"/>
-      <c r="AI43" s="19"/>
-      <c r="AJ43" s="18"/>
-      <c r="AK43" s="19"/>
-      <c r="AL43" s="18"/>
-      <c r="AM43" s="19"/>
-      <c r="AN43" s="20"/>
-      <c r="AO43" s="18"/>
-      <c r="AP43" s="19"/>
-      <c r="AQ43" s="18"/>
-      <c r="AR43" s="19"/>
-      <c r="AS43" s="18"/>
-      <c r="AT43" s="18"/>
-      <c r="AU43" s="19"/>
-      <c r="AV43" s="18"/>
-      <c r="AW43" s="19"/>
-      <c r="AX43" s="18"/>
-      <c r="AY43" s="19"/>
-      <c r="AZ43" s="20"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB44" s="24"/>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB45" s="24"/>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB46" s="24"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U47" s="15"/>
-      <c r="AB47" s="24"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB48" s="24"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB49" s="24"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB50" s="24"/>
+      <c r="U39" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7610,7 +7434,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CK50"/>
+  <dimension ref="A1:CK47"/>
   <sheetFormatPr defaultColWidth="8.76171875" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.36"/>
@@ -8104,19 +7928,16 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB12" s="24"/>
       <c r="AZ12" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB13" s="24"/>
       <c r="AW13" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB14" s="24"/>
       <c r="AZ14" s="4" t="n">
         <v>2</v>
       </c>
@@ -8125,14 +7946,12 @@
       <c r="N15" s="15"/>
       <c r="P15" s="16"/>
       <c r="Z15" s="15"/>
-      <c r="AB15" s="24"/>
       <c r="AW15" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U16" s="15"/>
-      <c r="AB16" s="24"/>
       <c r="AG16" s="15"/>
       <c r="AZ16" s="4" t="n">
         <v>2</v>
@@ -8142,7 +7961,6 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB17" s="24"/>
       <c r="AW17" s="3" t="n">
         <v>1</v>
       </c>
@@ -8152,7 +7970,6 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U18" s="15"/>
-      <c r="AB18" s="24"/>
       <c r="AG18" s="15"/>
       <c r="AZ18" s="4" t="n">
         <v>2</v>
@@ -8179,7 +7996,7 @@
       <c r="M19" s="19"/>
       <c r="N19" s="23"/>
       <c r="O19" s="19"/>
-      <c r="P19" s="25"/>
+      <c r="P19" s="20"/>
       <c r="Q19" s="18"/>
       <c r="R19" s="19"/>
       <c r="S19" s="18"/>
@@ -8191,7 +8008,7 @@
       <c r="Y19" s="23"/>
       <c r="Z19" s="18"/>
       <c r="AA19" s="19"/>
-      <c r="AB19" s="25"/>
+      <c r="AB19" s="20"/>
       <c r="AC19" s="18"/>
       <c r="AD19" s="19"/>
       <c r="AE19" s="18"/>
@@ -8225,8 +8042,6 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P20" s="24"/>
-      <c r="AB20" s="24"/>
       <c r="AK20" s="15"/>
       <c r="AN20" s="16" t="n">
         <v>1</v>
@@ -8236,7 +8051,6 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P21" s="24"/>
       <c r="AB21" s="16" t="n">
         <v>5</v>
       </c>
@@ -8245,8 +8059,6 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P22" s="24"/>
-      <c r="AB22" s="24"/>
       <c r="AK22" s="15"/>
       <c r="AN22" s="16" t="n">
         <v>1</v>
@@ -8256,8 +8068,6 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P23" s="24"/>
-      <c r="AB23" s="24"/>
       <c r="AD23" s="15" t="n">
         <v>3</v>
       </c>
@@ -8269,8 +8079,6 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P24" s="24"/>
-      <c r="AB24" s="24"/>
       <c r="AK24" s="15" t="n">
         <v>1</v>
       </c>
@@ -8282,11 +8090,9 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P25" s="24"/>
       <c r="Y25" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="AB25" s="24"/>
       <c r="AS25" s="2" t="n">
         <v>1</v>
       </c>
@@ -8295,8 +8101,6 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P26" s="24"/>
-      <c r="AB26" s="24"/>
       <c r="AK26" s="15" t="n">
         <v>1</v>
       </c>
@@ -8334,7 +8138,7 @@
       <c r="Y27" s="19"/>
       <c r="Z27" s="18"/>
       <c r="AA27" s="19"/>
-      <c r="AB27" s="25"/>
+      <c r="AB27" s="20"/>
       <c r="AC27" s="18"/>
       <c r="AD27" s="19"/>
       <c r="AE27" s="18"/>
@@ -8367,7 +8171,6 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB28" s="24"/>
       <c r="AK28" s="15" t="n">
         <v>1</v>
       </c>
@@ -8379,13 +8182,11 @@
       <c r="Y29" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="AB29" s="24"/>
       <c r="AN29" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB30" s="24"/>
       <c r="AK30" s="15" t="n">
         <v>1</v>
       </c>
@@ -8398,7 +8199,6 @@
       <c r="Z31" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="AB31" s="24"/>
       <c r="AP31" s="3" t="n">
         <v>1</v>
       </c>
@@ -8407,7 +8207,6 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB32" s="24"/>
       <c r="AG32" s="15" t="n">
         <v>1</v>
       </c>
@@ -8422,7 +8221,6 @@
       <c r="U33" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="AB33" s="24"/>
       <c r="AP33" s="3" t="n">
         <v>1</v>
       </c>
@@ -8431,7 +8229,6 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB34" s="24"/>
       <c r="AG34" s="15" t="n">
         <v>1</v>
       </c>
@@ -8502,7 +8299,6 @@
       <c r="AZ35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB36" s="24"/>
       <c r="AG36" s="15" t="n">
         <v>1</v>
       </c>
@@ -8515,13 +8311,11 @@
         <v>5</v>
       </c>
       <c r="V37" s="15"/>
-      <c r="AB37" s="24"/>
       <c r="AK37" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB38" s="24"/>
       <c r="AG38" s="15" t="n">
         <v>1</v>
       </c>
@@ -8539,7 +8333,6 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB40" s="24"/>
       <c r="AG40" s="15" t="n">
         <v>1</v>
       </c>
@@ -8552,7 +8345,6 @@
         <v>5</v>
       </c>
       <c r="V41" s="15"/>
-      <c r="AB41" s="24"/>
       <c r="AK41" s="3" t="n">
         <v>1</v>
       </c>
@@ -8595,7 +8387,7 @@
       <c r="Y43" s="19"/>
       <c r="Z43" s="18"/>
       <c r="AA43" s="19"/>
-      <c r="AB43" s="25"/>
+      <c r="AB43" s="20"/>
       <c r="AC43" s="18"/>
       <c r="AD43" s="19"/>
       <c r="AE43" s="18"/>
@@ -8624,13 +8416,11 @@
       <c r="AZ43" s="20"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB44" s="24"/>
       <c r="AU44" s="3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB45" s="24"/>
       <c r="AG45" s="15" t="n">
         <v>1</v>
       </c>
@@ -8640,22 +8430,9 @@
       <c r="AS45" s="2" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB46" s="24"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U47" s="15"/>
-      <c r="AB47" s="24"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB48" s="24"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB49" s="24"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB50" s="24"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -9167,19 +8944,16 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB12" s="24"/>
       <c r="AZ12" s="4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB13" s="24"/>
       <c r="AW13" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB14" s="24"/>
       <c r="AZ14" s="4" t="n">
         <v>2</v>
       </c>
@@ -9188,14 +8962,12 @@
       <c r="N15" s="15"/>
       <c r="P15" s="16"/>
       <c r="Z15" s="15"/>
-      <c r="AB15" s="24"/>
       <c r="AW15" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U16" s="15"/>
-      <c r="AB16" s="24"/>
       <c r="AG16" s="15"/>
       <c r="AZ16" s="4" t="n">
         <v>2</v>
@@ -9205,7 +8977,6 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB17" s="24"/>
       <c r="AW17" s="3" t="n">
         <v>1</v>
       </c>
@@ -9215,7 +8986,6 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="U18" s="15"/>
-      <c r="AB18" s="24"/>
       <c r="AG18" s="15"/>
       <c r="AZ18" s="4" t="n">
         <v>2</v>
@@ -9242,7 +9012,7 @@
       <c r="M19" s="19"/>
       <c r="N19" s="23"/>
       <c r="O19" s="19"/>
-      <c r="P19" s="25"/>
+      <c r="P19" s="20"/>
       <c r="Q19" s="18"/>
       <c r="R19" s="19"/>
       <c r="S19" s="18"/>
@@ -9254,7 +9024,7 @@
       <c r="Y19" s="23"/>
       <c r="Z19" s="18"/>
       <c r="AA19" s="19"/>
-      <c r="AB19" s="25"/>
+      <c r="AB19" s="20"/>
       <c r="AC19" s="18"/>
       <c r="AD19" s="19"/>
       <c r="AE19" s="18"/>
@@ -9288,8 +9058,6 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P20" s="24"/>
-      <c r="AB20" s="24"/>
       <c r="AK20" s="15"/>
       <c r="AN20" s="16" t="n">
         <v>1</v>
@@ -9299,7 +9067,6 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P21" s="24"/>
       <c r="AB21" s="16" t="n">
         <v>5</v>
       </c>
@@ -9308,8 +9075,6 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P22" s="24"/>
-      <c r="AB22" s="24"/>
       <c r="AK22" s="15"/>
       <c r="AN22" s="16" t="n">
         <v>1</v>
@@ -9319,8 +9084,6 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P23" s="24"/>
-      <c r="AB23" s="24"/>
       <c r="AD23" s="15" t="n">
         <v>3</v>
       </c>
@@ -9332,8 +9095,6 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P24" s="24"/>
-      <c r="AB24" s="24"/>
       <c r="AK24" s="15" t="n">
         <v>1</v>
       </c>
@@ -9345,11 +9106,9 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P25" s="24"/>
       <c r="Y25" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="AB25" s="24"/>
       <c r="AS25" s="2" t="n">
         <v>1</v>
       </c>
@@ -9358,8 +9117,6 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P26" s="24"/>
-      <c r="AB26" s="24"/>
       <c r="AK26" s="15" t="n">
         <v>1</v>
       </c>
@@ -9397,7 +9154,7 @@
       <c r="Y27" s="19"/>
       <c r="Z27" s="18"/>
       <c r="AA27" s="19"/>
-      <c r="AB27" s="25"/>
+      <c r="AB27" s="20"/>
       <c r="AC27" s="18"/>
       <c r="AD27" s="19"/>
       <c r="AE27" s="18"/>
@@ -9430,7 +9187,6 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB28" s="24"/>
       <c r="AK28" s="15" t="n">
         <v>1</v>
       </c>
@@ -9442,13 +9198,11 @@
       <c r="Y29" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="AB29" s="24"/>
       <c r="AN29" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB30" s="24"/>
       <c r="AK30" s="15" t="n">
         <v>1</v>
       </c>
@@ -9461,7 +9215,6 @@
       <c r="Z31" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="AB31" s="24"/>
       <c r="AP31" s="3" t="n">
         <v>1</v>
       </c>
@@ -9470,7 +9223,6 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB32" s="24"/>
       <c r="AG32" s="15" t="n">
         <v>1</v>
       </c>
@@ -9485,7 +9237,6 @@
       <c r="U33" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="AB33" s="24"/>
       <c r="AP33" s="3" t="n">
         <v>1</v>
       </c>
@@ -9494,7 +9245,6 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB34" s="24"/>
       <c r="AG34" s="15" t="n">
         <v>1</v>
       </c>
@@ -9565,7 +9315,6 @@
       <c r="AZ35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB36" s="24"/>
       <c r="AG36" s="15" t="n">
         <v>1</v>
       </c>
@@ -9578,13 +9327,11 @@
         <v>5</v>
       </c>
       <c r="V37" s="15"/>
-      <c r="AB37" s="24"/>
       <c r="AK37" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB38" s="24"/>
       <c r="AG38" s="15" t="n">
         <v>1</v>
       </c>
@@ -9603,7 +9350,6 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB40" s="24"/>
       <c r="AG40" s="15" t="n">
         <v>1</v>
       </c>
@@ -9619,7 +9365,6 @@
         <v>5</v>
       </c>
       <c r="V41" s="15"/>
-      <c r="AB41" s="24"/>
       <c r="AL41" s="2" t="n">
         <v>1</v>
       </c>
@@ -9699,7 +9444,6 @@
       <c r="AZ43" s="20"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB44" s="24"/>
       <c r="AG44" s="15" t="n">
         <v>1</v>
       </c>
@@ -9712,13 +9456,11 @@
         <v>5</v>
       </c>
       <c r="V45" s="15"/>
-      <c r="AB45" s="24"/>
       <c r="AK45" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB46" s="24"/>
       <c r="AG46" s="15" t="n">
         <v>1</v>
       </c>
@@ -9737,7 +9479,6 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB48" s="24"/>
       <c r="AG48" s="15" t="n">
         <v>1</v>
       </c>
@@ -9753,7 +9494,6 @@
         <v>5</v>
       </c>
       <c r="V49" s="15"/>
-      <c r="AB49" s="24"/>
       <c r="AL49" s="2" t="n">
         <v>1</v>
       </c>
@@ -9770,7 +9510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" s="24" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
         <v>2</v>
       </c>
@@ -9831,6 +9571,979 @@
       <c r="AX51" s="18"/>
       <c r="AY51" s="19"/>
       <c r="AZ51" s="20"/>
+      <c r="BA51" s="2"/>
+      <c r="BB51" s="3"/>
+      <c r="BC51" s="2"/>
+      <c r="BD51" s="3"/>
+      <c r="BE51" s="2"/>
+      <c r="BF51" s="2"/>
+      <c r="BG51" s="3"/>
+      <c r="BH51" s="2"/>
+      <c r="BI51" s="3"/>
+      <c r="BJ51" s="2"/>
+      <c r="BK51" s="3"/>
+      <c r="BL51" s="4"/>
+      <c r="BM51" s="2"/>
+      <c r="BN51" s="3"/>
+      <c r="BO51" s="2"/>
+      <c r="BP51" s="3"/>
+      <c r="BQ51" s="2"/>
+      <c r="BR51" s="2"/>
+      <c r="BS51" s="3"/>
+      <c r="BT51" s="2"/>
+      <c r="BU51" s="3"/>
+      <c r="BV51" s="2"/>
+      <c r="BW51" s="3"/>
+      <c r="BX51" s="4"/>
+      <c r="BY51" s="2"/>
+      <c r="BZ51" s="3"/>
+      <c r="CA51" s="2"/>
+      <c r="CB51" s="3"/>
+      <c r="CC51" s="2"/>
+      <c r="CD51" s="2"/>
+      <c r="CE51" s="3"/>
+      <c r="CF51" s="2"/>
+      <c r="CG51" s="3"/>
+      <c r="CH51" s="2"/>
+      <c r="CI51" s="3"/>
+      <c r="CJ51" s="4"/>
+      <c r="CK51" s="2"/>
+      <c r="CL51" s="1"/>
+      <c r="CM51" s="1"/>
+      <c r="CN51" s="1"/>
+      <c r="CO51" s="1"/>
+      <c r="CP51" s="1"/>
+      <c r="CQ51" s="1"/>
+      <c r="CR51" s="1"/>
+      <c r="CS51" s="1"/>
+      <c r="CT51" s="1"/>
+      <c r="CU51" s="1"/>
+      <c r="CV51" s="1"/>
+      <c r="CW51" s="1"/>
+      <c r="CX51" s="1"/>
+      <c r="CY51" s="1"/>
+      <c r="CZ51" s="1"/>
+      <c r="DA51" s="1"/>
+      <c r="DB51" s="1"/>
+      <c r="DC51" s="1"/>
+      <c r="DD51" s="1"/>
+      <c r="DE51" s="1"/>
+      <c r="DF51" s="1"/>
+      <c r="DG51" s="1"/>
+      <c r="DH51" s="1"/>
+      <c r="DI51" s="1"/>
+      <c r="DJ51" s="1"/>
+      <c r="DK51" s="1"/>
+      <c r="DL51" s="1"/>
+      <c r="DM51" s="1"/>
+      <c r="DN51" s="1"/>
+      <c r="DO51" s="1"/>
+      <c r="DP51" s="1"/>
+      <c r="DQ51" s="1"/>
+      <c r="DR51" s="1"/>
+      <c r="DS51" s="1"/>
+      <c r="DT51" s="1"/>
+      <c r="DU51" s="1"/>
+      <c r="DV51" s="1"/>
+      <c r="DW51" s="1"/>
+      <c r="DX51" s="1"/>
+      <c r="DY51" s="1"/>
+      <c r="DZ51" s="1"/>
+      <c r="EA51" s="1"/>
+      <c r="EB51" s="1"/>
+      <c r="EC51" s="1"/>
+      <c r="ED51" s="1"/>
+      <c r="EE51" s="1"/>
+      <c r="EF51" s="1"/>
+      <c r="EG51" s="1"/>
+      <c r="EH51" s="1"/>
+      <c r="EI51" s="1"/>
+      <c r="EJ51" s="1"/>
+      <c r="EK51" s="1"/>
+      <c r="EL51" s="1"/>
+      <c r="EM51" s="1"/>
+      <c r="EN51" s="1"/>
+      <c r="EO51" s="1"/>
+      <c r="EP51" s="1"/>
+      <c r="EQ51" s="1"/>
+      <c r="ER51" s="1"/>
+      <c r="ES51" s="1"/>
+      <c r="ET51" s="1"/>
+      <c r="EU51" s="1"/>
+      <c r="EV51" s="1"/>
+      <c r="EW51" s="1"/>
+      <c r="EX51" s="1"/>
+      <c r="EY51" s="1"/>
+      <c r="EZ51" s="1"/>
+      <c r="FA51" s="1"/>
+      <c r="FB51" s="1"/>
+      <c r="FC51" s="1"/>
+      <c r="FD51" s="1"/>
+      <c r="FE51" s="1"/>
+      <c r="FF51" s="1"/>
+      <c r="FG51" s="1"/>
+      <c r="FH51" s="1"/>
+      <c r="FI51" s="1"/>
+      <c r="FJ51" s="1"/>
+      <c r="FK51" s="1"/>
+      <c r="FL51" s="1"/>
+      <c r="FM51" s="1"/>
+      <c r="FN51" s="1"/>
+      <c r="FO51" s="1"/>
+      <c r="FP51" s="1"/>
+      <c r="FQ51" s="1"/>
+      <c r="FR51" s="1"/>
+      <c r="FS51" s="1"/>
+      <c r="FT51" s="1"/>
+      <c r="FU51" s="1"/>
+      <c r="FV51" s="1"/>
+      <c r="FW51" s="1"/>
+      <c r="FX51" s="1"/>
+      <c r="FY51" s="1"/>
+      <c r="FZ51" s="1"/>
+      <c r="GA51" s="1"/>
+      <c r="GB51" s="1"/>
+      <c r="GC51" s="1"/>
+      <c r="GD51" s="1"/>
+      <c r="GE51" s="1"/>
+      <c r="GF51" s="1"/>
+      <c r="GG51" s="1"/>
+      <c r="GH51" s="1"/>
+      <c r="GI51" s="1"/>
+      <c r="GJ51" s="1"/>
+      <c r="GK51" s="1"/>
+      <c r="GL51" s="1"/>
+      <c r="GM51" s="1"/>
+      <c r="GN51" s="1"/>
+      <c r="GO51" s="1"/>
+      <c r="GP51" s="1"/>
+      <c r="GQ51" s="1"/>
+      <c r="GR51" s="1"/>
+      <c r="GS51" s="1"/>
+      <c r="GT51" s="1"/>
+      <c r="GU51" s="1"/>
+      <c r="GV51" s="1"/>
+      <c r="GW51" s="1"/>
+      <c r="GX51" s="1"/>
+      <c r="GY51" s="1"/>
+      <c r="GZ51" s="1"/>
+      <c r="HA51" s="1"/>
+      <c r="HB51" s="1"/>
+      <c r="HC51" s="1"/>
+      <c r="HD51" s="1"/>
+      <c r="HE51" s="1"/>
+      <c r="HF51" s="1"/>
+      <c r="HG51" s="1"/>
+      <c r="HH51" s="1"/>
+      <c r="HI51" s="1"/>
+      <c r="HJ51" s="1"/>
+      <c r="HK51" s="1"/>
+      <c r="HL51" s="1"/>
+      <c r="HM51" s="1"/>
+      <c r="HN51" s="1"/>
+      <c r="HO51" s="1"/>
+      <c r="HP51" s="1"/>
+      <c r="HQ51" s="1"/>
+      <c r="HR51" s="1"/>
+      <c r="HS51" s="1"/>
+      <c r="HT51" s="1"/>
+      <c r="HU51" s="1"/>
+      <c r="HV51" s="1"/>
+      <c r="HW51" s="1"/>
+      <c r="HX51" s="1"/>
+      <c r="HY51" s="1"/>
+      <c r="HZ51" s="1"/>
+      <c r="IA51" s="1"/>
+      <c r="IB51" s="1"/>
+      <c r="IC51" s="1"/>
+      <c r="ID51" s="1"/>
+      <c r="IE51" s="1"/>
+      <c r="IF51" s="1"/>
+      <c r="IG51" s="1"/>
+      <c r="IH51" s="1"/>
+      <c r="II51" s="1"/>
+      <c r="IJ51" s="1"/>
+      <c r="IK51" s="1"/>
+      <c r="IL51" s="1"/>
+      <c r="IM51" s="1"/>
+      <c r="IN51" s="1"/>
+      <c r="IO51" s="1"/>
+      <c r="IP51" s="1"/>
+      <c r="IQ51" s="1"/>
+      <c r="IR51" s="1"/>
+      <c r="IS51" s="1"/>
+      <c r="IT51" s="1"/>
+      <c r="IU51" s="1"/>
+      <c r="IV51" s="1"/>
+      <c r="IW51" s="1"/>
+      <c r="IX51" s="1"/>
+      <c r="IY51" s="1"/>
+      <c r="IZ51" s="1"/>
+      <c r="JA51" s="1"/>
+      <c r="JB51" s="1"/>
+      <c r="JC51" s="1"/>
+      <c r="JD51" s="1"/>
+      <c r="JE51" s="1"/>
+      <c r="JF51" s="1"/>
+      <c r="JG51" s="1"/>
+      <c r="JH51" s="1"/>
+      <c r="JI51" s="1"/>
+      <c r="JJ51" s="1"/>
+      <c r="JK51" s="1"/>
+      <c r="JL51" s="1"/>
+      <c r="JM51" s="1"/>
+      <c r="JN51" s="1"/>
+      <c r="JO51" s="1"/>
+      <c r="JP51" s="1"/>
+      <c r="JQ51" s="1"/>
+      <c r="JR51" s="1"/>
+      <c r="JS51" s="1"/>
+      <c r="JT51" s="1"/>
+      <c r="JU51" s="1"/>
+      <c r="JV51" s="1"/>
+      <c r="JW51" s="1"/>
+      <c r="JX51" s="1"/>
+      <c r="JY51" s="1"/>
+      <c r="JZ51" s="1"/>
+      <c r="KA51" s="1"/>
+      <c r="KB51" s="1"/>
+      <c r="KC51" s="1"/>
+      <c r="KD51" s="1"/>
+      <c r="KE51" s="1"/>
+      <c r="KF51" s="1"/>
+      <c r="KG51" s="1"/>
+      <c r="KH51" s="1"/>
+      <c r="KI51" s="1"/>
+      <c r="KJ51" s="1"/>
+      <c r="KK51" s="1"/>
+      <c r="KL51" s="1"/>
+      <c r="KM51" s="1"/>
+      <c r="KN51" s="1"/>
+      <c r="KO51" s="1"/>
+      <c r="KP51" s="1"/>
+      <c r="KQ51" s="1"/>
+      <c r="KR51" s="1"/>
+      <c r="KS51" s="1"/>
+      <c r="KT51" s="1"/>
+      <c r="KU51" s="1"/>
+      <c r="KV51" s="1"/>
+      <c r="KW51" s="1"/>
+      <c r="KX51" s="1"/>
+      <c r="KY51" s="1"/>
+      <c r="KZ51" s="1"/>
+      <c r="LA51" s="1"/>
+      <c r="LB51" s="1"/>
+      <c r="LC51" s="1"/>
+      <c r="LD51" s="1"/>
+      <c r="LE51" s="1"/>
+      <c r="LF51" s="1"/>
+      <c r="LG51" s="1"/>
+      <c r="LH51" s="1"/>
+      <c r="LI51" s="1"/>
+      <c r="LJ51" s="1"/>
+      <c r="LK51" s="1"/>
+      <c r="LL51" s="1"/>
+      <c r="LM51" s="1"/>
+      <c r="LN51" s="1"/>
+      <c r="LO51" s="1"/>
+      <c r="LP51" s="1"/>
+      <c r="LQ51" s="1"/>
+      <c r="LR51" s="1"/>
+      <c r="LS51" s="1"/>
+      <c r="LT51" s="1"/>
+      <c r="LU51" s="1"/>
+      <c r="LV51" s="1"/>
+      <c r="LW51" s="1"/>
+      <c r="LX51" s="1"/>
+      <c r="LY51" s="1"/>
+      <c r="LZ51" s="1"/>
+      <c r="MA51" s="1"/>
+      <c r="MB51" s="1"/>
+      <c r="MC51" s="1"/>
+      <c r="MD51" s="1"/>
+      <c r="ME51" s="1"/>
+      <c r="MF51" s="1"/>
+      <c r="MG51" s="1"/>
+      <c r="MH51" s="1"/>
+      <c r="MI51" s="1"/>
+      <c r="MJ51" s="1"/>
+      <c r="MK51" s="1"/>
+      <c r="ML51" s="1"/>
+      <c r="MM51" s="1"/>
+      <c r="MN51" s="1"/>
+      <c r="MO51" s="1"/>
+      <c r="MP51" s="1"/>
+      <c r="MQ51" s="1"/>
+      <c r="MR51" s="1"/>
+      <c r="MS51" s="1"/>
+      <c r="MT51" s="1"/>
+      <c r="MU51" s="1"/>
+      <c r="MV51" s="1"/>
+      <c r="MW51" s="1"/>
+      <c r="MX51" s="1"/>
+      <c r="MY51" s="1"/>
+      <c r="MZ51" s="1"/>
+      <c r="NA51" s="1"/>
+      <c r="NB51" s="1"/>
+      <c r="NC51" s="1"/>
+      <c r="ND51" s="1"/>
+      <c r="NE51" s="1"/>
+      <c r="NF51" s="1"/>
+      <c r="NG51" s="1"/>
+      <c r="NH51" s="1"/>
+      <c r="NI51" s="1"/>
+      <c r="NJ51" s="1"/>
+      <c r="NK51" s="1"/>
+      <c r="NL51" s="1"/>
+      <c r="NM51" s="1"/>
+      <c r="NN51" s="1"/>
+      <c r="NO51" s="1"/>
+      <c r="NP51" s="1"/>
+      <c r="NQ51" s="1"/>
+      <c r="NR51" s="1"/>
+      <c r="NS51" s="1"/>
+      <c r="NT51" s="1"/>
+      <c r="NU51" s="1"/>
+      <c r="NV51" s="1"/>
+      <c r="NW51" s="1"/>
+      <c r="NX51" s="1"/>
+      <c r="NY51" s="1"/>
+      <c r="NZ51" s="1"/>
+      <c r="OA51" s="1"/>
+      <c r="OB51" s="1"/>
+      <c r="OC51" s="1"/>
+      <c r="OD51" s="1"/>
+      <c r="OE51" s="1"/>
+      <c r="OF51" s="1"/>
+      <c r="OG51" s="1"/>
+      <c r="OH51" s="1"/>
+      <c r="OI51" s="1"/>
+      <c r="OJ51" s="1"/>
+      <c r="OK51" s="1"/>
+      <c r="OL51" s="1"/>
+      <c r="OM51" s="1"/>
+      <c r="ON51" s="1"/>
+      <c r="OO51" s="1"/>
+      <c r="OP51" s="1"/>
+      <c r="OQ51" s="1"/>
+      <c r="OR51" s="1"/>
+      <c r="OS51" s="1"/>
+      <c r="OT51" s="1"/>
+      <c r="OU51" s="1"/>
+      <c r="OV51" s="1"/>
+      <c r="OW51" s="1"/>
+      <c r="OX51" s="1"/>
+      <c r="OY51" s="1"/>
+      <c r="OZ51" s="1"/>
+      <c r="PA51" s="1"/>
+      <c r="PB51" s="1"/>
+      <c r="PC51" s="1"/>
+      <c r="PD51" s="1"/>
+      <c r="PE51" s="1"/>
+      <c r="PF51" s="1"/>
+      <c r="PG51" s="1"/>
+      <c r="PH51" s="1"/>
+      <c r="PI51" s="1"/>
+      <c r="PJ51" s="1"/>
+      <c r="PK51" s="1"/>
+      <c r="PL51" s="1"/>
+      <c r="PM51" s="1"/>
+      <c r="PN51" s="1"/>
+      <c r="PO51" s="1"/>
+      <c r="PP51" s="1"/>
+      <c r="PQ51" s="1"/>
+      <c r="PR51" s="1"/>
+      <c r="PS51" s="1"/>
+      <c r="PT51" s="1"/>
+      <c r="PU51" s="1"/>
+      <c r="PV51" s="1"/>
+      <c r="PW51" s="1"/>
+      <c r="PX51" s="1"/>
+      <c r="PY51" s="1"/>
+      <c r="PZ51" s="1"/>
+      <c r="QA51" s="1"/>
+      <c r="QB51" s="1"/>
+      <c r="QC51" s="1"/>
+      <c r="QD51" s="1"/>
+      <c r="QE51" s="1"/>
+      <c r="QF51" s="1"/>
+      <c r="QG51" s="1"/>
+      <c r="QH51" s="1"/>
+      <c r="QI51" s="1"/>
+      <c r="QJ51" s="1"/>
+      <c r="QK51" s="1"/>
+      <c r="QL51" s="1"/>
+      <c r="QM51" s="1"/>
+      <c r="QN51" s="1"/>
+      <c r="QO51" s="1"/>
+      <c r="QP51" s="1"/>
+      <c r="QQ51" s="1"/>
+      <c r="QR51" s="1"/>
+      <c r="QS51" s="1"/>
+      <c r="QT51" s="1"/>
+      <c r="QU51" s="1"/>
+      <c r="QV51" s="1"/>
+      <c r="QW51" s="1"/>
+      <c r="QX51" s="1"/>
+      <c r="QY51" s="1"/>
+      <c r="QZ51" s="1"/>
+      <c r="RA51" s="1"/>
+      <c r="RB51" s="1"/>
+      <c r="RC51" s="1"/>
+      <c r="RD51" s="1"/>
+      <c r="RE51" s="1"/>
+      <c r="RF51" s="1"/>
+      <c r="RG51" s="1"/>
+      <c r="RH51" s="1"/>
+      <c r="RI51" s="1"/>
+      <c r="RJ51" s="1"/>
+      <c r="RK51" s="1"/>
+      <c r="RL51" s="1"/>
+      <c r="RM51" s="1"/>
+      <c r="RN51" s="1"/>
+      <c r="RO51" s="1"/>
+      <c r="RP51" s="1"/>
+      <c r="RQ51" s="1"/>
+      <c r="RR51" s="1"/>
+      <c r="RS51" s="1"/>
+      <c r="RT51" s="1"/>
+      <c r="RU51" s="1"/>
+      <c r="RV51" s="1"/>
+      <c r="RW51" s="1"/>
+      <c r="RX51" s="1"/>
+      <c r="RY51" s="1"/>
+      <c r="RZ51" s="1"/>
+      <c r="SA51" s="1"/>
+      <c r="SB51" s="1"/>
+      <c r="SC51" s="1"/>
+      <c r="SD51" s="1"/>
+      <c r="SE51" s="1"/>
+      <c r="SF51" s="1"/>
+      <c r="SG51" s="1"/>
+      <c r="SH51" s="1"/>
+      <c r="SI51" s="1"/>
+      <c r="SJ51" s="1"/>
+      <c r="SK51" s="1"/>
+      <c r="SL51" s="1"/>
+      <c r="SM51" s="1"/>
+      <c r="SN51" s="1"/>
+      <c r="SO51" s="1"/>
+      <c r="SP51" s="1"/>
+      <c r="SQ51" s="1"/>
+      <c r="SR51" s="1"/>
+      <c r="SS51" s="1"/>
+      <c r="ST51" s="1"/>
+      <c r="SU51" s="1"/>
+      <c r="SV51" s="1"/>
+      <c r="SW51" s="1"/>
+      <c r="SX51" s="1"/>
+      <c r="SY51" s="1"/>
+      <c r="SZ51" s="1"/>
+      <c r="TA51" s="1"/>
+      <c r="TB51" s="1"/>
+      <c r="TC51" s="1"/>
+      <c r="TD51" s="1"/>
+      <c r="TE51" s="1"/>
+      <c r="TF51" s="1"/>
+      <c r="TG51" s="1"/>
+      <c r="TH51" s="1"/>
+      <c r="TI51" s="1"/>
+      <c r="TJ51" s="1"/>
+      <c r="TK51" s="1"/>
+      <c r="TL51" s="1"/>
+      <c r="TM51" s="1"/>
+      <c r="TN51" s="1"/>
+      <c r="TO51" s="1"/>
+      <c r="TP51" s="1"/>
+      <c r="TQ51" s="1"/>
+      <c r="TR51" s="1"/>
+      <c r="TS51" s="1"/>
+      <c r="TT51" s="1"/>
+      <c r="TU51" s="1"/>
+      <c r="TV51" s="1"/>
+      <c r="TW51" s="1"/>
+      <c r="TX51" s="1"/>
+      <c r="TY51" s="1"/>
+      <c r="TZ51" s="1"/>
+      <c r="UA51" s="1"/>
+      <c r="UB51" s="1"/>
+      <c r="UC51" s="1"/>
+      <c r="UD51" s="1"/>
+      <c r="UE51" s="1"/>
+      <c r="UF51" s="1"/>
+      <c r="UG51" s="1"/>
+      <c r="UH51" s="1"/>
+      <c r="UI51" s="1"/>
+      <c r="UJ51" s="1"/>
+      <c r="UK51" s="1"/>
+      <c r="UL51" s="1"/>
+      <c r="UM51" s="1"/>
+      <c r="UN51" s="1"/>
+      <c r="UO51" s="1"/>
+      <c r="UP51" s="1"/>
+      <c r="UQ51" s="1"/>
+      <c r="UR51" s="1"/>
+      <c r="US51" s="1"/>
+      <c r="UT51" s="1"/>
+      <c r="UU51" s="1"/>
+      <c r="UV51" s="1"/>
+      <c r="UW51" s="1"/>
+      <c r="UX51" s="1"/>
+      <c r="UY51" s="1"/>
+      <c r="UZ51" s="1"/>
+      <c r="VA51" s="1"/>
+      <c r="VB51" s="1"/>
+      <c r="VC51" s="1"/>
+      <c r="VD51" s="1"/>
+      <c r="VE51" s="1"/>
+      <c r="VF51" s="1"/>
+      <c r="VG51" s="1"/>
+      <c r="VH51" s="1"/>
+      <c r="VI51" s="1"/>
+      <c r="VJ51" s="1"/>
+      <c r="VK51" s="1"/>
+      <c r="VL51" s="1"/>
+      <c r="VM51" s="1"/>
+      <c r="VN51" s="1"/>
+      <c r="VO51" s="1"/>
+      <c r="VP51" s="1"/>
+      <c r="VQ51" s="1"/>
+      <c r="VR51" s="1"/>
+      <c r="VS51" s="1"/>
+      <c r="VT51" s="1"/>
+      <c r="VU51" s="1"/>
+      <c r="VV51" s="1"/>
+      <c r="VW51" s="1"/>
+      <c r="VX51" s="1"/>
+      <c r="VY51" s="1"/>
+      <c r="VZ51" s="1"/>
+      <c r="WA51" s="1"/>
+      <c r="WB51" s="1"/>
+      <c r="WC51" s="1"/>
+      <c r="WD51" s="1"/>
+      <c r="WE51" s="1"/>
+      <c r="WF51" s="1"/>
+      <c r="WG51" s="1"/>
+      <c r="WH51" s="1"/>
+      <c r="WI51" s="1"/>
+      <c r="WJ51" s="1"/>
+      <c r="WK51" s="1"/>
+      <c r="WL51" s="1"/>
+      <c r="WM51" s="1"/>
+      <c r="WN51" s="1"/>
+      <c r="WO51" s="1"/>
+      <c r="WP51" s="1"/>
+      <c r="WQ51" s="1"/>
+      <c r="WR51" s="1"/>
+      <c r="WS51" s="1"/>
+      <c r="WT51" s="1"/>
+      <c r="WU51" s="1"/>
+      <c r="WV51" s="1"/>
+      <c r="WW51" s="1"/>
+      <c r="WX51" s="1"/>
+      <c r="WY51" s="1"/>
+      <c r="WZ51" s="1"/>
+      <c r="XA51" s="1"/>
+      <c r="XB51" s="1"/>
+      <c r="XC51" s="1"/>
+      <c r="XD51" s="1"/>
+      <c r="XE51" s="1"/>
+      <c r="XF51" s="1"/>
+      <c r="XG51" s="1"/>
+      <c r="XH51" s="1"/>
+      <c r="XI51" s="1"/>
+      <c r="XJ51" s="1"/>
+      <c r="XK51" s="1"/>
+      <c r="XL51" s="1"/>
+      <c r="XM51" s="1"/>
+      <c r="XN51" s="1"/>
+      <c r="XO51" s="1"/>
+      <c r="XP51" s="1"/>
+      <c r="XQ51" s="1"/>
+      <c r="XR51" s="1"/>
+      <c r="XS51" s="1"/>
+      <c r="XT51" s="1"/>
+      <c r="XU51" s="1"/>
+      <c r="XV51" s="1"/>
+      <c r="XW51" s="1"/>
+      <c r="XX51" s="1"/>
+      <c r="XY51" s="1"/>
+      <c r="XZ51" s="1"/>
+      <c r="YA51" s="1"/>
+      <c r="YB51" s="1"/>
+      <c r="YC51" s="1"/>
+      <c r="YD51" s="1"/>
+      <c r="YE51" s="1"/>
+      <c r="YF51" s="1"/>
+      <c r="YG51" s="1"/>
+      <c r="YH51" s="1"/>
+      <c r="YI51" s="1"/>
+      <c r="YJ51" s="1"/>
+      <c r="YK51" s="1"/>
+      <c r="YL51" s="1"/>
+      <c r="YM51" s="1"/>
+      <c r="YN51" s="1"/>
+      <c r="YO51" s="1"/>
+      <c r="YP51" s="1"/>
+      <c r="YQ51" s="1"/>
+      <c r="YR51" s="1"/>
+      <c r="YS51" s="1"/>
+      <c r="YT51" s="1"/>
+      <c r="YU51" s="1"/>
+      <c r="YV51" s="1"/>
+      <c r="YW51" s="1"/>
+      <c r="YX51" s="1"/>
+      <c r="YY51" s="1"/>
+      <c r="YZ51" s="1"/>
+      <c r="ZA51" s="1"/>
+      <c r="ZB51" s="1"/>
+      <c r="ZC51" s="1"/>
+      <c r="ZD51" s="1"/>
+      <c r="ZE51" s="1"/>
+      <c r="ZF51" s="1"/>
+      <c r="ZG51" s="1"/>
+      <c r="ZH51" s="1"/>
+      <c r="ZI51" s="1"/>
+      <c r="ZJ51" s="1"/>
+      <c r="ZK51" s="1"/>
+      <c r="ZL51" s="1"/>
+      <c r="ZM51" s="1"/>
+      <c r="ZN51" s="1"/>
+      <c r="ZO51" s="1"/>
+      <c r="ZP51" s="1"/>
+      <c r="ZQ51" s="1"/>
+      <c r="ZR51" s="1"/>
+      <c r="ZS51" s="1"/>
+      <c r="ZT51" s="1"/>
+      <c r="ZU51" s="1"/>
+      <c r="ZV51" s="1"/>
+      <c r="ZW51" s="1"/>
+      <c r="ZX51" s="1"/>
+      <c r="ZY51" s="1"/>
+      <c r="ZZ51" s="1"/>
+      <c r="AAA51" s="1"/>
+      <c r="AAB51" s="1"/>
+      <c r="AAC51" s="1"/>
+      <c r="AAD51" s="1"/>
+      <c r="AAE51" s="1"/>
+      <c r="AAF51" s="1"/>
+      <c r="AAG51" s="1"/>
+      <c r="AAH51" s="1"/>
+      <c r="AAI51" s="1"/>
+      <c r="AAJ51" s="1"/>
+      <c r="AAK51" s="1"/>
+      <c r="AAL51" s="1"/>
+      <c r="AAM51" s="1"/>
+      <c r="AAN51" s="1"/>
+      <c r="AAO51" s="1"/>
+      <c r="AAP51" s="1"/>
+      <c r="AAQ51" s="1"/>
+      <c r="AAR51" s="1"/>
+      <c r="AAS51" s="1"/>
+      <c r="AAT51" s="1"/>
+      <c r="AAU51" s="1"/>
+      <c r="AAV51" s="1"/>
+      <c r="AAW51" s="1"/>
+      <c r="AAX51" s="1"/>
+      <c r="AAY51" s="1"/>
+      <c r="AAZ51" s="1"/>
+      <c r="ABA51" s="1"/>
+      <c r="ABB51" s="1"/>
+      <c r="ABC51" s="1"/>
+      <c r="ABD51" s="1"/>
+      <c r="ABE51" s="1"/>
+      <c r="ABF51" s="1"/>
+      <c r="ABG51" s="1"/>
+      <c r="ABH51" s="1"/>
+      <c r="ABI51" s="1"/>
+      <c r="ABJ51" s="1"/>
+      <c r="ABK51" s="1"/>
+      <c r="ABL51" s="1"/>
+      <c r="ABM51" s="1"/>
+      <c r="ABN51" s="1"/>
+      <c r="ABO51" s="1"/>
+      <c r="ABP51" s="1"/>
+      <c r="ABQ51" s="1"/>
+      <c r="ABR51" s="1"/>
+      <c r="ABS51" s="1"/>
+      <c r="ABT51" s="1"/>
+      <c r="ABU51" s="1"/>
+      <c r="ABV51" s="1"/>
+      <c r="ABW51" s="1"/>
+      <c r="ABX51" s="1"/>
+      <c r="ABY51" s="1"/>
+      <c r="ABZ51" s="1"/>
+      <c r="ACA51" s="1"/>
+      <c r="ACB51" s="1"/>
+      <c r="ACC51" s="1"/>
+      <c r="ACD51" s="1"/>
+      <c r="ACE51" s="1"/>
+      <c r="ACF51" s="1"/>
+      <c r="ACG51" s="1"/>
+      <c r="ACH51" s="1"/>
+      <c r="ACI51" s="1"/>
+      <c r="ACJ51" s="1"/>
+      <c r="ACK51" s="1"/>
+      <c r="ACL51" s="1"/>
+      <c r="ACM51" s="1"/>
+      <c r="ACN51" s="1"/>
+      <c r="ACO51" s="1"/>
+      <c r="ACP51" s="1"/>
+      <c r="ACQ51" s="1"/>
+      <c r="ACR51" s="1"/>
+      <c r="ACS51" s="1"/>
+      <c r="ACT51" s="1"/>
+      <c r="ACU51" s="1"/>
+      <c r="ACV51" s="1"/>
+      <c r="ACW51" s="1"/>
+      <c r="ACX51" s="1"/>
+      <c r="ACY51" s="1"/>
+      <c r="ACZ51" s="1"/>
+      <c r="ADA51" s="1"/>
+      <c r="ADB51" s="1"/>
+      <c r="ADC51" s="1"/>
+      <c r="ADD51" s="1"/>
+      <c r="ADE51" s="1"/>
+      <c r="ADF51" s="1"/>
+      <c r="ADG51" s="1"/>
+      <c r="ADH51" s="1"/>
+      <c r="ADI51" s="1"/>
+      <c r="ADJ51" s="1"/>
+      <c r="ADK51" s="1"/>
+      <c r="ADL51" s="1"/>
+      <c r="ADM51" s="1"/>
+      <c r="ADN51" s="1"/>
+      <c r="ADO51" s="1"/>
+      <c r="ADP51" s="1"/>
+      <c r="ADQ51" s="1"/>
+      <c r="ADR51" s="1"/>
+      <c r="ADS51" s="1"/>
+      <c r="ADT51" s="1"/>
+      <c r="ADU51" s="1"/>
+      <c r="ADV51" s="1"/>
+      <c r="ADW51" s="1"/>
+      <c r="ADX51" s="1"/>
+      <c r="ADY51" s="1"/>
+      <c r="ADZ51" s="1"/>
+      <c r="AEA51" s="1"/>
+      <c r="AEB51" s="1"/>
+      <c r="AEC51" s="1"/>
+      <c r="AED51" s="1"/>
+      <c r="AEE51" s="1"/>
+      <c r="AEF51" s="1"/>
+      <c r="AEG51" s="1"/>
+      <c r="AEH51" s="1"/>
+      <c r="AEI51" s="1"/>
+      <c r="AEJ51" s="1"/>
+      <c r="AEK51" s="1"/>
+      <c r="AEL51" s="1"/>
+      <c r="AEM51" s="1"/>
+      <c r="AEN51" s="1"/>
+      <c r="AEO51" s="1"/>
+      <c r="AEP51" s="1"/>
+      <c r="AEQ51" s="1"/>
+      <c r="AER51" s="1"/>
+      <c r="AES51" s="1"/>
+      <c r="AET51" s="1"/>
+      <c r="AEU51" s="1"/>
+      <c r="AEV51" s="1"/>
+      <c r="AEW51" s="1"/>
+      <c r="AEX51" s="1"/>
+      <c r="AEY51" s="1"/>
+      <c r="AEZ51" s="1"/>
+      <c r="AFA51" s="1"/>
+      <c r="AFB51" s="1"/>
+      <c r="AFC51" s="1"/>
+      <c r="AFD51" s="1"/>
+      <c r="AFE51" s="1"/>
+      <c r="AFF51" s="1"/>
+      <c r="AFG51" s="1"/>
+      <c r="AFH51" s="1"/>
+      <c r="AFI51" s="1"/>
+      <c r="AFJ51" s="1"/>
+      <c r="AFK51" s="1"/>
+      <c r="AFL51" s="1"/>
+      <c r="AFM51" s="1"/>
+      <c r="AFN51" s="1"/>
+      <c r="AFO51" s="1"/>
+      <c r="AFP51" s="1"/>
+      <c r="AFQ51" s="1"/>
+      <c r="AFR51" s="1"/>
+      <c r="AFS51" s="1"/>
+      <c r="AFT51" s="1"/>
+      <c r="AFU51" s="1"/>
+      <c r="AFV51" s="1"/>
+      <c r="AFW51" s="1"/>
+      <c r="AFX51" s="1"/>
+      <c r="AFY51" s="1"/>
+      <c r="AFZ51" s="1"/>
+      <c r="AGA51" s="1"/>
+      <c r="AGB51" s="1"/>
+      <c r="AGC51" s="1"/>
+      <c r="AGD51" s="1"/>
+      <c r="AGE51" s="1"/>
+      <c r="AGF51" s="1"/>
+      <c r="AGG51" s="1"/>
+      <c r="AGH51" s="1"/>
+      <c r="AGI51" s="1"/>
+      <c r="AGJ51" s="1"/>
+      <c r="AGK51" s="1"/>
+      <c r="AGL51" s="1"/>
+      <c r="AGM51" s="1"/>
+      <c r="AGN51" s="1"/>
+      <c r="AGO51" s="1"/>
+      <c r="AGP51" s="1"/>
+      <c r="AGQ51" s="1"/>
+      <c r="AGR51" s="1"/>
+      <c r="AGS51" s="1"/>
+      <c r="AGT51" s="1"/>
+      <c r="AGU51" s="1"/>
+      <c r="AGV51" s="1"/>
+      <c r="AGW51" s="1"/>
+      <c r="AGX51" s="1"/>
+      <c r="AGY51" s="1"/>
+      <c r="AGZ51" s="1"/>
+      <c r="AHA51" s="1"/>
+      <c r="AHB51" s="1"/>
+      <c r="AHC51" s="1"/>
+      <c r="AHD51" s="1"/>
+      <c r="AHE51" s="1"/>
+      <c r="AHF51" s="1"/>
+      <c r="AHG51" s="1"/>
+      <c r="AHH51" s="1"/>
+      <c r="AHI51" s="1"/>
+      <c r="AHJ51" s="1"/>
+      <c r="AHK51" s="1"/>
+      <c r="AHL51" s="1"/>
+      <c r="AHM51" s="1"/>
+      <c r="AHN51" s="1"/>
+      <c r="AHO51" s="1"/>
+      <c r="AHP51" s="1"/>
+      <c r="AHQ51" s="1"/>
+      <c r="AHR51" s="1"/>
+      <c r="AHS51" s="1"/>
+      <c r="AHT51" s="1"/>
+      <c r="AHU51" s="1"/>
+      <c r="AHV51" s="1"/>
+      <c r="AHW51" s="1"/>
+      <c r="AHX51" s="1"/>
+      <c r="AHY51" s="1"/>
+      <c r="AHZ51" s="1"/>
+      <c r="AIA51" s="1"/>
+      <c r="AIB51" s="1"/>
+      <c r="AIC51" s="1"/>
+      <c r="AID51" s="1"/>
+      <c r="AIE51" s="1"/>
+      <c r="AIF51" s="1"/>
+      <c r="AIG51" s="1"/>
+      <c r="AIH51" s="1"/>
+      <c r="AII51" s="1"/>
+      <c r="AIJ51" s="1"/>
+      <c r="AIK51" s="1"/>
+      <c r="AIL51" s="1"/>
+      <c r="AIM51" s="1"/>
+      <c r="AIN51" s="1"/>
+      <c r="AIO51" s="1"/>
+      <c r="AIP51" s="1"/>
+      <c r="AIQ51" s="1"/>
+      <c r="AIR51" s="1"/>
+      <c r="AIS51" s="1"/>
+      <c r="AIT51" s="1"/>
+      <c r="AIU51" s="1"/>
+      <c r="AIV51" s="1"/>
+      <c r="AIW51" s="1"/>
+      <c r="AIX51" s="1"/>
+      <c r="AIY51" s="1"/>
+      <c r="AIZ51" s="1"/>
+      <c r="AJA51" s="1"/>
+      <c r="AJB51" s="1"/>
+      <c r="AJC51" s="1"/>
+      <c r="AJD51" s="1"/>
+      <c r="AJE51" s="1"/>
+      <c r="AJF51" s="1"/>
+      <c r="AJG51" s="1"/>
+      <c r="AJH51" s="1"/>
+      <c r="AJI51" s="1"/>
+      <c r="AJJ51" s="1"/>
+      <c r="AJK51" s="1"/>
+      <c r="AJL51" s="1"/>
+      <c r="AJM51" s="1"/>
+      <c r="AJN51" s="1"/>
+      <c r="AJO51" s="1"/>
+      <c r="AJP51" s="1"/>
+      <c r="AJQ51" s="1"/>
+      <c r="AJR51" s="1"/>
+      <c r="AJS51" s="1"/>
+      <c r="AJT51" s="1"/>
+      <c r="AJU51" s="1"/>
+      <c r="AJV51" s="1"/>
+      <c r="AJW51" s="1"/>
+      <c r="AJX51" s="1"/>
+      <c r="AJY51" s="1"/>
+      <c r="AJZ51" s="1"/>
+      <c r="AKA51" s="1"/>
+      <c r="AKB51" s="1"/>
+      <c r="AKC51" s="1"/>
+      <c r="AKD51" s="1"/>
+      <c r="AKE51" s="1"/>
+      <c r="AKF51" s="1"/>
+      <c r="AKG51" s="1"/>
+      <c r="AKH51" s="1"/>
+      <c r="AKI51" s="1"/>
+      <c r="AKJ51" s="1"/>
+      <c r="AKK51" s="1"/>
+      <c r="AKL51" s="1"/>
+      <c r="AKM51" s="1"/>
+      <c r="AKN51" s="1"/>
+      <c r="AKO51" s="1"/>
+      <c r="AKP51" s="1"/>
+      <c r="AKQ51" s="1"/>
+      <c r="AKR51" s="1"/>
+      <c r="AKS51" s="1"/>
+      <c r="AKT51" s="1"/>
+      <c r="AKU51" s="1"/>
+      <c r="AKV51" s="1"/>
+      <c r="AKW51" s="1"/>
+      <c r="AKX51" s="1"/>
+      <c r="AKY51" s="1"/>
+      <c r="AKZ51" s="1"/>
+      <c r="ALA51" s="1"/>
+      <c r="ALB51" s="1"/>
+      <c r="ALC51" s="1"/>
+      <c r="ALD51" s="1"/>
+      <c r="ALE51" s="1"/>
+      <c r="ALF51" s="1"/>
+      <c r="ALG51" s="1"/>
+      <c r="ALH51" s="1"/>
+      <c r="ALI51" s="1"/>
+      <c r="ALJ51" s="1"/>
+      <c r="ALK51" s="1"/>
+      <c r="ALL51" s="1"/>
+      <c r="ALM51" s="1"/>
+      <c r="ALN51" s="1"/>
+      <c r="ALO51" s="1"/>
+      <c r="ALP51" s="1"/>
+      <c r="ALQ51" s="1"/>
+      <c r="ALR51" s="1"/>
+      <c r="ALS51" s="1"/>
+      <c r="ALT51" s="1"/>
+      <c r="ALU51" s="1"/>
+      <c r="ALV51" s="1"/>
+      <c r="ALW51" s="1"/>
+      <c r="ALX51" s="1"/>
+      <c r="ALY51" s="1"/>
+      <c r="ALZ51" s="1"/>
+      <c r="AMA51" s="1"/>
+      <c r="AMB51" s="1"/>
+      <c r="AMC51" s="1"/>
+      <c r="AMD51" s="1"/>
+      <c r="AME51" s="1"/>
+      <c r="AMF51" s="1"/>
+      <c r="AMG51" s="1"/>
+      <c r="AMH51" s="1"/>
+      <c r="AMI51" s="1"/>
+      <c r="AMJ51" s="1"/>
+      <c r="AMK51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AG52" s="15" t="n">
@@ -9888,7 +10601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" s="26" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" s="24" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="17" t="s">
         <v>2</v>
       </c>
@@ -10984,7 +11697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" s="26" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="17" t="s">
         <v>2</v>
       </c>
@@ -13030,1039 +13743,1039 @@
       <c r="AJ70" s="15"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="B71" s="28"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="28"/>
-      <c r="J71" s="28"/>
-      <c r="K71" s="29"/>
-      <c r="L71" s="28"/>
-      <c r="M71" s="29"/>
-      <c r="N71" s="28"/>
-      <c r="O71" s="29"/>
-      <c r="P71" s="30"/>
-      <c r="Q71" s="28"/>
-      <c r="R71" s="29"/>
-      <c r="S71" s="28"/>
-      <c r="T71" s="29"/>
-      <c r="U71" s="28"/>
-      <c r="V71" s="28"/>
-      <c r="W71" s="29"/>
-      <c r="X71" s="28"/>
-      <c r="Y71" s="29"/>
-      <c r="Z71" s="28"/>
-      <c r="AA71" s="29"/>
-      <c r="AB71" s="30"/>
-      <c r="AC71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD71" s="29"/>
-      <c r="AE71" s="28"/>
-      <c r="AF71" s="29"/>
-      <c r="AG71" s="28"/>
-      <c r="AH71" s="28"/>
-      <c r="AI71" s="29"/>
-      <c r="AJ71" s="27"/>
-      <c r="AK71" s="29"/>
-      <c r="AL71" s="28"/>
-      <c r="AM71" s="29"/>
-      <c r="AN71" s="30"/>
-      <c r="AO71" s="27"/>
-      <c r="AP71" s="29"/>
-      <c r="AQ71" s="28"/>
-      <c r="AR71" s="29"/>
-      <c r="AS71" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT71" s="28"/>
-      <c r="AU71" s="29"/>
-      <c r="AV71" s="28"/>
-      <c r="AW71" s="29"/>
-      <c r="AX71" s="28"/>
-      <c r="AY71" s="29"/>
-      <c r="AZ71" s="30"/>
-      <c r="BA71" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB71" s="29"/>
-      <c r="BC71" s="28"/>
-      <c r="BD71" s="29"/>
-      <c r="BE71" s="28"/>
-      <c r="BF71" s="28"/>
-      <c r="BG71" s="29"/>
-      <c r="BH71" s="28"/>
-      <c r="BI71" s="29"/>
-      <c r="BJ71" s="28"/>
-      <c r="BK71" s="29"/>
-      <c r="BL71" s="30"/>
-      <c r="BM71" s="28"/>
-      <c r="BN71" s="29"/>
-      <c r="BO71" s="28"/>
-      <c r="BP71" s="29"/>
-      <c r="BQ71" s="28"/>
-      <c r="BR71" s="28"/>
-      <c r="BS71" s="29"/>
-      <c r="BT71" s="28"/>
-      <c r="BU71" s="29"/>
-      <c r="BV71" s="28"/>
-      <c r="BW71" s="29"/>
-      <c r="BX71" s="30"/>
-      <c r="BY71" s="28"/>
-      <c r="BZ71" s="29"/>
-      <c r="CA71" s="28"/>
-      <c r="CB71" s="29"/>
-      <c r="CC71" s="28"/>
-      <c r="CD71" s="28"/>
-      <c r="CE71" s="29"/>
-      <c r="CF71" s="28"/>
-      <c r="CG71" s="29"/>
-      <c r="CH71" s="28"/>
-      <c r="CI71" s="29"/>
-      <c r="CJ71" s="30"/>
-      <c r="CK71" s="28"/>
-      <c r="CL71" s="33"/>
-      <c r="CM71" s="33"/>
-      <c r="CN71" s="33"/>
-      <c r="CO71" s="33"/>
-      <c r="CP71" s="33"/>
-      <c r="CQ71" s="33"/>
-      <c r="CR71" s="33"/>
-      <c r="CS71" s="33"/>
-      <c r="CT71" s="33"/>
-      <c r="CU71" s="33"/>
-      <c r="CV71" s="33"/>
-      <c r="CW71" s="33"/>
-      <c r="CX71" s="33"/>
-      <c r="CY71" s="33"/>
-      <c r="CZ71" s="33"/>
-      <c r="DA71" s="33"/>
-      <c r="DB71" s="33"/>
-      <c r="DC71" s="33"/>
-      <c r="DD71" s="33"/>
-      <c r="DE71" s="33"/>
-      <c r="DF71" s="33"/>
-      <c r="DG71" s="33"/>
-      <c r="DH71" s="33"/>
-      <c r="DI71" s="33"/>
-      <c r="DJ71" s="33"/>
-      <c r="DK71" s="33"/>
-      <c r="DL71" s="33"/>
-      <c r="DM71" s="33"/>
-      <c r="DN71" s="33"/>
-      <c r="DO71" s="33"/>
-      <c r="DP71" s="33"/>
-      <c r="DQ71" s="33"/>
-      <c r="DR71" s="33"/>
-      <c r="DS71" s="33"/>
-      <c r="DT71" s="33"/>
-      <c r="DU71" s="33"/>
-      <c r="DV71" s="33"/>
-      <c r="DW71" s="33"/>
-      <c r="DX71" s="33"/>
-      <c r="DY71" s="33"/>
-      <c r="DZ71" s="33"/>
-      <c r="EA71" s="33"/>
-      <c r="EB71" s="33"/>
-      <c r="EC71" s="33"/>
-      <c r="ED71" s="33"/>
-      <c r="EE71" s="33"/>
-      <c r="EF71" s="33"/>
-      <c r="EG71" s="33"/>
-      <c r="EH71" s="33"/>
-      <c r="EI71" s="33"/>
-      <c r="EJ71" s="33"/>
-      <c r="EK71" s="33"/>
-      <c r="EL71" s="33"/>
-      <c r="EM71" s="33"/>
-      <c r="EN71" s="33"/>
-      <c r="EO71" s="33"/>
-      <c r="EP71" s="33"/>
-      <c r="EQ71" s="33"/>
-      <c r="ER71" s="33"/>
-      <c r="ES71" s="33"/>
-      <c r="ET71" s="33"/>
-      <c r="EU71" s="33"/>
-      <c r="EV71" s="33"/>
-      <c r="EW71" s="33"/>
-      <c r="EX71" s="33"/>
-      <c r="EY71" s="33"/>
-      <c r="EZ71" s="33"/>
-      <c r="FA71" s="33"/>
-      <c r="FB71" s="33"/>
-      <c r="FC71" s="33"/>
-      <c r="FD71" s="33"/>
-      <c r="FE71" s="33"/>
-      <c r="FF71" s="33"/>
-      <c r="FG71" s="33"/>
-      <c r="FH71" s="33"/>
-      <c r="FI71" s="33"/>
-      <c r="FJ71" s="33"/>
-      <c r="FK71" s="33"/>
-      <c r="FL71" s="33"/>
-      <c r="FM71" s="33"/>
-      <c r="FN71" s="33"/>
-      <c r="FO71" s="33"/>
-      <c r="FP71" s="33"/>
-      <c r="FQ71" s="33"/>
-      <c r="FR71" s="33"/>
-      <c r="FS71" s="33"/>
-      <c r="FT71" s="33"/>
-      <c r="FU71" s="33"/>
-      <c r="FV71" s="33"/>
-      <c r="FW71" s="33"/>
-      <c r="FX71" s="33"/>
-      <c r="FY71" s="33"/>
-      <c r="FZ71" s="33"/>
-      <c r="GA71" s="33"/>
-      <c r="GB71" s="33"/>
-      <c r="GC71" s="33"/>
-      <c r="GD71" s="33"/>
-      <c r="GE71" s="33"/>
-      <c r="GF71" s="33"/>
-      <c r="GG71" s="33"/>
-      <c r="GH71" s="33"/>
-      <c r="GI71" s="33"/>
-      <c r="GJ71" s="33"/>
-      <c r="GK71" s="33"/>
-      <c r="GL71" s="33"/>
-      <c r="GM71" s="33"/>
-      <c r="GN71" s="33"/>
-      <c r="GO71" s="33"/>
-      <c r="GP71" s="33"/>
-      <c r="GQ71" s="33"/>
-      <c r="GR71" s="33"/>
-      <c r="GS71" s="33"/>
-      <c r="GT71" s="33"/>
-      <c r="GU71" s="33"/>
-      <c r="GV71" s="33"/>
-      <c r="GW71" s="33"/>
-      <c r="GX71" s="33"/>
-      <c r="GY71" s="33"/>
-      <c r="GZ71" s="33"/>
-      <c r="HA71" s="33"/>
-      <c r="HB71" s="33"/>
-      <c r="HC71" s="33"/>
-      <c r="HD71" s="33"/>
-      <c r="HE71" s="33"/>
-      <c r="HF71" s="33"/>
-      <c r="HG71" s="33"/>
-      <c r="HH71" s="33"/>
-      <c r="HI71" s="33"/>
-      <c r="HJ71" s="33"/>
-      <c r="HK71" s="33"/>
-      <c r="HL71" s="33"/>
-      <c r="HM71" s="33"/>
-      <c r="HN71" s="33"/>
-      <c r="HO71" s="33"/>
-      <c r="HP71" s="33"/>
-      <c r="HQ71" s="33"/>
-      <c r="HR71" s="33"/>
-      <c r="HS71" s="33"/>
-      <c r="HT71" s="33"/>
-      <c r="HU71" s="33"/>
-      <c r="HV71" s="33"/>
-      <c r="HW71" s="33"/>
-      <c r="HX71" s="33"/>
-      <c r="HY71" s="33"/>
-      <c r="HZ71" s="33"/>
-      <c r="IA71" s="33"/>
-      <c r="IB71" s="33"/>
-      <c r="IC71" s="33"/>
-      <c r="ID71" s="33"/>
-      <c r="IE71" s="33"/>
-      <c r="IF71" s="33"/>
-      <c r="IG71" s="33"/>
-      <c r="IH71" s="33"/>
-      <c r="II71" s="33"/>
-      <c r="IJ71" s="33"/>
-      <c r="IK71" s="33"/>
-      <c r="IL71" s="33"/>
-      <c r="IM71" s="33"/>
-      <c r="IN71" s="33"/>
-      <c r="IO71" s="33"/>
-      <c r="IP71" s="33"/>
-      <c r="IQ71" s="33"/>
-      <c r="IR71" s="33"/>
-      <c r="IS71" s="33"/>
-      <c r="IT71" s="33"/>
-      <c r="IU71" s="33"/>
-      <c r="IV71" s="33"/>
-      <c r="IW71" s="33"/>
-      <c r="IX71" s="33"/>
-      <c r="IY71" s="33"/>
-      <c r="IZ71" s="33"/>
-      <c r="JA71" s="33"/>
-      <c r="JB71" s="33"/>
-      <c r="JC71" s="33"/>
-      <c r="JD71" s="33"/>
-      <c r="JE71" s="33"/>
-      <c r="JF71" s="33"/>
-      <c r="JG71" s="33"/>
-      <c r="JH71" s="33"/>
-      <c r="JI71" s="33"/>
-      <c r="JJ71" s="33"/>
-      <c r="JK71" s="33"/>
-      <c r="JL71" s="33"/>
-      <c r="JM71" s="33"/>
-      <c r="JN71" s="33"/>
-      <c r="JO71" s="33"/>
-      <c r="JP71" s="33"/>
-      <c r="JQ71" s="33"/>
-      <c r="JR71" s="33"/>
-      <c r="JS71" s="33"/>
-      <c r="JT71" s="33"/>
-      <c r="JU71" s="33"/>
-      <c r="JV71" s="33"/>
-      <c r="JW71" s="33"/>
-      <c r="JX71" s="33"/>
-      <c r="JY71" s="33"/>
-      <c r="JZ71" s="33"/>
-      <c r="KA71" s="33"/>
-      <c r="KB71" s="33"/>
-      <c r="KC71" s="33"/>
-      <c r="KD71" s="33"/>
-      <c r="KE71" s="33"/>
-      <c r="KF71" s="33"/>
-      <c r="KG71" s="33"/>
-      <c r="KH71" s="33"/>
-      <c r="KI71" s="33"/>
-      <c r="KJ71" s="33"/>
-      <c r="KK71" s="33"/>
-      <c r="KL71" s="33"/>
-      <c r="KM71" s="33"/>
-      <c r="KN71" s="33"/>
-      <c r="KO71" s="33"/>
-      <c r="KP71" s="33"/>
-      <c r="KQ71" s="33"/>
-      <c r="KR71" s="33"/>
-      <c r="KS71" s="33"/>
-      <c r="KT71" s="33"/>
-      <c r="KU71" s="33"/>
-      <c r="KV71" s="33"/>
-      <c r="KW71" s="33"/>
-      <c r="KX71" s="33"/>
-      <c r="KY71" s="33"/>
-      <c r="KZ71" s="33"/>
-      <c r="LA71" s="33"/>
-      <c r="LB71" s="33"/>
-      <c r="LC71" s="33"/>
-      <c r="LD71" s="33"/>
-      <c r="LE71" s="33"/>
-      <c r="LF71" s="33"/>
-      <c r="LG71" s="33"/>
-      <c r="LH71" s="33"/>
-      <c r="LI71" s="33"/>
-      <c r="LJ71" s="33"/>
-      <c r="LK71" s="33"/>
-      <c r="LL71" s="33"/>
-      <c r="LM71" s="33"/>
-      <c r="LN71" s="33"/>
-      <c r="LO71" s="33"/>
-      <c r="LP71" s="33"/>
-      <c r="LQ71" s="33"/>
-      <c r="LR71" s="33"/>
-      <c r="LS71" s="33"/>
-      <c r="LT71" s="33"/>
-      <c r="LU71" s="33"/>
-      <c r="LV71" s="33"/>
-      <c r="LW71" s="33"/>
-      <c r="LX71" s="33"/>
-      <c r="LY71" s="33"/>
-      <c r="LZ71" s="33"/>
-      <c r="MA71" s="33"/>
-      <c r="MB71" s="33"/>
-      <c r="MC71" s="33"/>
-      <c r="MD71" s="33"/>
-      <c r="ME71" s="33"/>
-      <c r="MF71" s="33"/>
-      <c r="MG71" s="33"/>
-      <c r="MH71" s="33"/>
-      <c r="MI71" s="33"/>
-      <c r="MJ71" s="33"/>
-      <c r="MK71" s="33"/>
-      <c r="ML71" s="33"/>
-      <c r="MM71" s="33"/>
-      <c r="MN71" s="33"/>
-      <c r="MO71" s="33"/>
-      <c r="MP71" s="33"/>
-      <c r="MQ71" s="33"/>
-      <c r="MR71" s="33"/>
-      <c r="MS71" s="33"/>
-      <c r="MT71" s="33"/>
-      <c r="MU71" s="33"/>
-      <c r="MV71" s="33"/>
-      <c r="MW71" s="33"/>
-      <c r="MX71" s="33"/>
-      <c r="MY71" s="33"/>
-      <c r="MZ71" s="33"/>
-      <c r="NA71" s="33"/>
-      <c r="NB71" s="33"/>
-      <c r="NC71" s="33"/>
-      <c r="ND71" s="33"/>
-      <c r="NE71" s="33"/>
-      <c r="NF71" s="33"/>
-      <c r="NG71" s="33"/>
-      <c r="NH71" s="33"/>
-      <c r="NI71" s="33"/>
-      <c r="NJ71" s="33"/>
-      <c r="NK71" s="33"/>
-      <c r="NL71" s="33"/>
-      <c r="NM71" s="33"/>
-      <c r="NN71" s="33"/>
-      <c r="NO71" s="33"/>
-      <c r="NP71" s="33"/>
-      <c r="NQ71" s="33"/>
-      <c r="NR71" s="33"/>
-      <c r="NS71" s="33"/>
-      <c r="NT71" s="33"/>
-      <c r="NU71" s="33"/>
-      <c r="NV71" s="33"/>
-      <c r="NW71" s="33"/>
-      <c r="NX71" s="33"/>
-      <c r="NY71" s="33"/>
-      <c r="NZ71" s="33"/>
-      <c r="OA71" s="33"/>
-      <c r="OB71" s="33"/>
-      <c r="OC71" s="33"/>
-      <c r="OD71" s="33"/>
-      <c r="OE71" s="33"/>
-      <c r="OF71" s="33"/>
-      <c r="OG71" s="33"/>
-      <c r="OH71" s="33"/>
-      <c r="OI71" s="33"/>
-      <c r="OJ71" s="33"/>
-      <c r="OK71" s="33"/>
-      <c r="OL71" s="33"/>
-      <c r="OM71" s="33"/>
-      <c r="ON71" s="33"/>
-      <c r="OO71" s="33"/>
-      <c r="OP71" s="33"/>
-      <c r="OQ71" s="33"/>
-      <c r="OR71" s="33"/>
-      <c r="OS71" s="33"/>
-      <c r="OT71" s="33"/>
-      <c r="OU71" s="33"/>
-      <c r="OV71" s="33"/>
-      <c r="OW71" s="33"/>
-      <c r="OX71" s="33"/>
-      <c r="OY71" s="33"/>
-      <c r="OZ71" s="33"/>
-      <c r="PA71" s="33"/>
-      <c r="PB71" s="33"/>
-      <c r="PC71" s="33"/>
-      <c r="PD71" s="33"/>
-      <c r="PE71" s="33"/>
-      <c r="PF71" s="33"/>
-      <c r="PG71" s="33"/>
-      <c r="PH71" s="33"/>
-      <c r="PI71" s="33"/>
-      <c r="PJ71" s="33"/>
-      <c r="PK71" s="33"/>
-      <c r="PL71" s="33"/>
-      <c r="PM71" s="33"/>
-      <c r="PN71" s="33"/>
-      <c r="PO71" s="33"/>
-      <c r="PP71" s="33"/>
-      <c r="PQ71" s="33"/>
-      <c r="PR71" s="33"/>
-      <c r="PS71" s="33"/>
-      <c r="PT71" s="33"/>
-      <c r="PU71" s="33"/>
-      <c r="PV71" s="33"/>
-      <c r="PW71" s="33"/>
-      <c r="PX71" s="33"/>
-      <c r="PY71" s="33"/>
-      <c r="PZ71" s="33"/>
-      <c r="QA71" s="33"/>
-      <c r="QB71" s="33"/>
-      <c r="QC71" s="33"/>
-      <c r="QD71" s="33"/>
-      <c r="QE71" s="33"/>
-      <c r="QF71" s="33"/>
-      <c r="QG71" s="33"/>
-      <c r="QH71" s="33"/>
-      <c r="QI71" s="33"/>
-      <c r="QJ71" s="33"/>
-      <c r="QK71" s="33"/>
-      <c r="QL71" s="33"/>
-      <c r="QM71" s="33"/>
-      <c r="QN71" s="33"/>
-      <c r="QO71" s="33"/>
-      <c r="QP71" s="33"/>
-      <c r="QQ71" s="33"/>
-      <c r="QR71" s="33"/>
-      <c r="QS71" s="33"/>
-      <c r="QT71" s="33"/>
-      <c r="QU71" s="33"/>
-      <c r="QV71" s="33"/>
-      <c r="QW71" s="33"/>
-      <c r="QX71" s="33"/>
-      <c r="QY71" s="33"/>
-      <c r="QZ71" s="33"/>
-      <c r="RA71" s="33"/>
-      <c r="RB71" s="33"/>
-      <c r="RC71" s="33"/>
-      <c r="RD71" s="33"/>
-      <c r="RE71" s="33"/>
-      <c r="RF71" s="33"/>
-      <c r="RG71" s="33"/>
-      <c r="RH71" s="33"/>
-      <c r="RI71" s="33"/>
-      <c r="RJ71" s="33"/>
-      <c r="RK71" s="33"/>
-      <c r="RL71" s="33"/>
-      <c r="RM71" s="33"/>
-      <c r="RN71" s="33"/>
-      <c r="RO71" s="33"/>
-      <c r="RP71" s="33"/>
-      <c r="RQ71" s="33"/>
-      <c r="RR71" s="33"/>
-      <c r="RS71" s="33"/>
-      <c r="RT71" s="33"/>
-      <c r="RU71" s="33"/>
-      <c r="RV71" s="33"/>
-      <c r="RW71" s="33"/>
-      <c r="RX71" s="33"/>
-      <c r="RY71" s="33"/>
-      <c r="RZ71" s="33"/>
-      <c r="SA71" s="33"/>
-      <c r="SB71" s="33"/>
-      <c r="SC71" s="33"/>
-      <c r="SD71" s="33"/>
-      <c r="SE71" s="33"/>
-      <c r="SF71" s="33"/>
-      <c r="SG71" s="33"/>
-      <c r="SH71" s="33"/>
-      <c r="SI71" s="33"/>
-      <c r="SJ71" s="33"/>
-      <c r="SK71" s="33"/>
-      <c r="SL71" s="33"/>
-      <c r="SM71" s="33"/>
-      <c r="SN71" s="33"/>
-      <c r="SO71" s="33"/>
-      <c r="SP71" s="33"/>
-      <c r="SQ71" s="33"/>
-      <c r="SR71" s="33"/>
-      <c r="SS71" s="33"/>
-      <c r="ST71" s="33"/>
-      <c r="SU71" s="33"/>
-      <c r="SV71" s="33"/>
-      <c r="SW71" s="33"/>
-      <c r="SX71" s="33"/>
-      <c r="SY71" s="33"/>
-      <c r="SZ71" s="33"/>
-      <c r="TA71" s="33"/>
-      <c r="TB71" s="33"/>
-      <c r="TC71" s="33"/>
-      <c r="TD71" s="33"/>
-      <c r="TE71" s="33"/>
-      <c r="TF71" s="33"/>
-      <c r="TG71" s="33"/>
-      <c r="TH71" s="33"/>
-      <c r="TI71" s="33"/>
-      <c r="TJ71" s="33"/>
-      <c r="TK71" s="33"/>
-      <c r="TL71" s="33"/>
-      <c r="TM71" s="33"/>
-      <c r="TN71" s="33"/>
-      <c r="TO71" s="33"/>
-      <c r="TP71" s="33"/>
-      <c r="TQ71" s="33"/>
-      <c r="TR71" s="33"/>
-      <c r="TS71" s="33"/>
-      <c r="TT71" s="33"/>
-      <c r="TU71" s="33"/>
-      <c r="TV71" s="33"/>
-      <c r="TW71" s="33"/>
-      <c r="TX71" s="33"/>
-      <c r="TY71" s="33"/>
-      <c r="TZ71" s="33"/>
-      <c r="UA71" s="33"/>
-      <c r="UB71" s="33"/>
-      <c r="UC71" s="33"/>
-      <c r="UD71" s="33"/>
-      <c r="UE71" s="33"/>
-      <c r="UF71" s="33"/>
-      <c r="UG71" s="33"/>
-      <c r="UH71" s="33"/>
-      <c r="UI71" s="33"/>
-      <c r="UJ71" s="33"/>
-      <c r="UK71" s="33"/>
-      <c r="UL71" s="33"/>
-      <c r="UM71" s="33"/>
-      <c r="UN71" s="33"/>
-      <c r="UO71" s="33"/>
-      <c r="UP71" s="33"/>
-      <c r="UQ71" s="33"/>
-      <c r="UR71" s="33"/>
-      <c r="US71" s="33"/>
-      <c r="UT71" s="33"/>
-      <c r="UU71" s="33"/>
-      <c r="UV71" s="33"/>
-      <c r="UW71" s="33"/>
-      <c r="UX71" s="33"/>
-      <c r="UY71" s="33"/>
-      <c r="UZ71" s="33"/>
-      <c r="VA71" s="33"/>
-      <c r="VB71" s="33"/>
-      <c r="VC71" s="33"/>
-      <c r="VD71" s="33"/>
-      <c r="VE71" s="33"/>
-      <c r="VF71" s="33"/>
-      <c r="VG71" s="33"/>
-      <c r="VH71" s="33"/>
-      <c r="VI71" s="33"/>
-      <c r="VJ71" s="33"/>
-      <c r="VK71" s="33"/>
-      <c r="VL71" s="33"/>
-      <c r="VM71" s="33"/>
-      <c r="VN71" s="33"/>
-      <c r="VO71" s="33"/>
-      <c r="VP71" s="33"/>
-      <c r="VQ71" s="33"/>
-      <c r="VR71" s="33"/>
-      <c r="VS71" s="33"/>
-      <c r="VT71" s="33"/>
-      <c r="VU71" s="33"/>
-      <c r="VV71" s="33"/>
-      <c r="VW71" s="33"/>
-      <c r="VX71" s="33"/>
-      <c r="VY71" s="33"/>
-      <c r="VZ71" s="33"/>
-      <c r="WA71" s="33"/>
-      <c r="WB71" s="33"/>
-      <c r="WC71" s="33"/>
-      <c r="WD71" s="33"/>
-      <c r="WE71" s="33"/>
-      <c r="WF71" s="33"/>
-      <c r="WG71" s="33"/>
-      <c r="WH71" s="33"/>
-      <c r="WI71" s="33"/>
-      <c r="WJ71" s="33"/>
-      <c r="WK71" s="33"/>
-      <c r="WL71" s="33"/>
-      <c r="WM71" s="33"/>
-      <c r="WN71" s="33"/>
-      <c r="WO71" s="33"/>
-      <c r="WP71" s="33"/>
-      <c r="WQ71" s="33"/>
-      <c r="WR71" s="33"/>
-      <c r="WS71" s="33"/>
-      <c r="WT71" s="33"/>
-      <c r="WU71" s="33"/>
-      <c r="WV71" s="33"/>
-      <c r="WW71" s="33"/>
-      <c r="WX71" s="33"/>
-      <c r="WY71" s="33"/>
-      <c r="WZ71" s="33"/>
-      <c r="XA71" s="33"/>
-      <c r="XB71" s="33"/>
-      <c r="XC71" s="33"/>
-      <c r="XD71" s="33"/>
-      <c r="XE71" s="33"/>
-      <c r="XF71" s="33"/>
-      <c r="XG71" s="33"/>
-      <c r="XH71" s="33"/>
-      <c r="XI71" s="33"/>
-      <c r="XJ71" s="33"/>
-      <c r="XK71" s="33"/>
-      <c r="XL71" s="33"/>
-      <c r="XM71" s="33"/>
-      <c r="XN71" s="33"/>
-      <c r="XO71" s="33"/>
-      <c r="XP71" s="33"/>
-      <c r="XQ71" s="33"/>
-      <c r="XR71" s="33"/>
-      <c r="XS71" s="33"/>
-      <c r="XT71" s="33"/>
-      <c r="XU71" s="33"/>
-      <c r="XV71" s="33"/>
-      <c r="XW71" s="33"/>
-      <c r="XX71" s="33"/>
-      <c r="XY71" s="33"/>
-      <c r="XZ71" s="33"/>
-      <c r="YA71" s="33"/>
-      <c r="YB71" s="33"/>
-      <c r="YC71" s="33"/>
-      <c r="YD71" s="33"/>
-      <c r="YE71" s="33"/>
-      <c r="YF71" s="33"/>
-      <c r="YG71" s="33"/>
-      <c r="YH71" s="33"/>
-      <c r="YI71" s="33"/>
-      <c r="YJ71" s="33"/>
-      <c r="YK71" s="33"/>
-      <c r="YL71" s="33"/>
-      <c r="YM71" s="33"/>
-      <c r="YN71" s="33"/>
-      <c r="YO71" s="33"/>
-      <c r="YP71" s="33"/>
-      <c r="YQ71" s="33"/>
-      <c r="YR71" s="33"/>
-      <c r="YS71" s="33"/>
-      <c r="YT71" s="33"/>
-      <c r="YU71" s="33"/>
-      <c r="YV71" s="33"/>
-      <c r="YW71" s="33"/>
-      <c r="YX71" s="33"/>
-      <c r="YY71" s="33"/>
-      <c r="YZ71" s="33"/>
-      <c r="ZA71" s="33"/>
-      <c r="ZB71" s="33"/>
-      <c r="ZC71" s="33"/>
-      <c r="ZD71" s="33"/>
-      <c r="ZE71" s="33"/>
-      <c r="ZF71" s="33"/>
-      <c r="ZG71" s="33"/>
-      <c r="ZH71" s="33"/>
-      <c r="ZI71" s="33"/>
-      <c r="ZJ71" s="33"/>
-      <c r="ZK71" s="33"/>
-      <c r="ZL71" s="33"/>
-      <c r="ZM71" s="33"/>
-      <c r="ZN71" s="33"/>
-      <c r="ZO71" s="33"/>
-      <c r="ZP71" s="33"/>
-      <c r="ZQ71" s="33"/>
-      <c r="ZR71" s="33"/>
-      <c r="ZS71" s="33"/>
-      <c r="ZT71" s="33"/>
-      <c r="ZU71" s="33"/>
-      <c r="ZV71" s="33"/>
-      <c r="ZW71" s="33"/>
-      <c r="ZX71" s="33"/>
-      <c r="ZY71" s="33"/>
-      <c r="ZZ71" s="33"/>
-      <c r="AAA71" s="33"/>
-      <c r="AAB71" s="33"/>
-      <c r="AAC71" s="33"/>
-      <c r="AAD71" s="33"/>
-      <c r="AAE71" s="33"/>
-      <c r="AAF71" s="33"/>
-      <c r="AAG71" s="33"/>
-      <c r="AAH71" s="33"/>
-      <c r="AAI71" s="33"/>
-      <c r="AAJ71" s="33"/>
-      <c r="AAK71" s="33"/>
-      <c r="AAL71" s="33"/>
-      <c r="AAM71" s="33"/>
-      <c r="AAN71" s="33"/>
-      <c r="AAO71" s="33"/>
-      <c r="AAP71" s="33"/>
-      <c r="AAQ71" s="33"/>
-      <c r="AAR71" s="33"/>
-      <c r="AAS71" s="33"/>
-      <c r="AAT71" s="33"/>
-      <c r="AAU71" s="33"/>
-      <c r="AAV71" s="33"/>
-      <c r="AAW71" s="33"/>
-      <c r="AAX71" s="33"/>
-      <c r="AAY71" s="33"/>
-      <c r="AAZ71" s="33"/>
-      <c r="ABA71" s="33"/>
-      <c r="ABB71" s="33"/>
-      <c r="ABC71" s="33"/>
-      <c r="ABD71" s="33"/>
-      <c r="ABE71" s="33"/>
-      <c r="ABF71" s="33"/>
-      <c r="ABG71" s="33"/>
-      <c r="ABH71" s="33"/>
-      <c r="ABI71" s="33"/>
-      <c r="ABJ71" s="33"/>
-      <c r="ABK71" s="33"/>
-      <c r="ABL71" s="33"/>
-      <c r="ABM71" s="33"/>
-      <c r="ABN71" s="33"/>
-      <c r="ABO71" s="33"/>
-      <c r="ABP71" s="33"/>
-      <c r="ABQ71" s="33"/>
-      <c r="ABR71" s="33"/>
-      <c r="ABS71" s="33"/>
-      <c r="ABT71" s="33"/>
-      <c r="ABU71" s="33"/>
-      <c r="ABV71" s="33"/>
-      <c r="ABW71" s="33"/>
-      <c r="ABX71" s="33"/>
-      <c r="ABY71" s="33"/>
-      <c r="ABZ71" s="33"/>
-      <c r="ACA71" s="33"/>
-      <c r="ACB71" s="33"/>
-      <c r="ACC71" s="33"/>
-      <c r="ACD71" s="33"/>
-      <c r="ACE71" s="33"/>
-      <c r="ACF71" s="33"/>
-      <c r="ACG71" s="33"/>
-      <c r="ACH71" s="33"/>
-      <c r="ACI71" s="33"/>
-      <c r="ACJ71" s="33"/>
-      <c r="ACK71" s="33"/>
-      <c r="ACL71" s="33"/>
-      <c r="ACM71" s="33"/>
-      <c r="ACN71" s="33"/>
-      <c r="ACO71" s="33"/>
-      <c r="ACP71" s="33"/>
-      <c r="ACQ71" s="33"/>
-      <c r="ACR71" s="33"/>
-      <c r="ACS71" s="33"/>
-      <c r="ACT71" s="33"/>
-      <c r="ACU71" s="33"/>
-      <c r="ACV71" s="33"/>
-      <c r="ACW71" s="33"/>
-      <c r="ACX71" s="33"/>
-      <c r="ACY71" s="33"/>
-      <c r="ACZ71" s="33"/>
-      <c r="ADA71" s="33"/>
-      <c r="ADB71" s="33"/>
-      <c r="ADC71" s="33"/>
-      <c r="ADD71" s="33"/>
-      <c r="ADE71" s="33"/>
-      <c r="ADF71" s="33"/>
-      <c r="ADG71" s="33"/>
-      <c r="ADH71" s="33"/>
-      <c r="ADI71" s="33"/>
-      <c r="ADJ71" s="33"/>
-      <c r="ADK71" s="33"/>
-      <c r="ADL71" s="33"/>
-      <c r="ADM71" s="33"/>
-      <c r="ADN71" s="33"/>
-      <c r="ADO71" s="33"/>
-      <c r="ADP71" s="33"/>
-      <c r="ADQ71" s="33"/>
-      <c r="ADR71" s="33"/>
-      <c r="ADS71" s="33"/>
-      <c r="ADT71" s="33"/>
-      <c r="ADU71" s="33"/>
-      <c r="ADV71" s="33"/>
-      <c r="ADW71" s="33"/>
-      <c r="ADX71" s="33"/>
-      <c r="ADY71" s="33"/>
-      <c r="ADZ71" s="33"/>
-      <c r="AEA71" s="33"/>
-      <c r="AEB71" s="33"/>
-      <c r="AEC71" s="33"/>
-      <c r="AED71" s="33"/>
-      <c r="AEE71" s="33"/>
-      <c r="AEF71" s="33"/>
-      <c r="AEG71" s="33"/>
-      <c r="AEH71" s="33"/>
-      <c r="AEI71" s="33"/>
-      <c r="AEJ71" s="33"/>
-      <c r="AEK71" s="33"/>
-      <c r="AEL71" s="33"/>
-      <c r="AEM71" s="33"/>
-      <c r="AEN71" s="33"/>
-      <c r="AEO71" s="33"/>
-      <c r="AEP71" s="33"/>
-      <c r="AEQ71" s="33"/>
-      <c r="AER71" s="33"/>
-      <c r="AES71" s="33"/>
-      <c r="AET71" s="33"/>
-      <c r="AEU71" s="33"/>
-      <c r="AEV71" s="33"/>
-      <c r="AEW71" s="33"/>
-      <c r="AEX71" s="33"/>
-      <c r="AEY71" s="33"/>
-      <c r="AEZ71" s="33"/>
-      <c r="AFA71" s="33"/>
-      <c r="AFB71" s="33"/>
-      <c r="AFC71" s="33"/>
-      <c r="AFD71" s="33"/>
-      <c r="AFE71" s="33"/>
-      <c r="AFF71" s="33"/>
-      <c r="AFG71" s="33"/>
-      <c r="AFH71" s="33"/>
-      <c r="AFI71" s="33"/>
-      <c r="AFJ71" s="33"/>
-      <c r="AFK71" s="33"/>
-      <c r="AFL71" s="33"/>
-      <c r="AFM71" s="33"/>
-      <c r="AFN71" s="33"/>
-      <c r="AFO71" s="33"/>
-      <c r="AFP71" s="33"/>
-      <c r="AFQ71" s="33"/>
-      <c r="AFR71" s="33"/>
-      <c r="AFS71" s="33"/>
-      <c r="AFT71" s="33"/>
-      <c r="AFU71" s="33"/>
-      <c r="AFV71" s="33"/>
-      <c r="AFW71" s="33"/>
-      <c r="AFX71" s="33"/>
-      <c r="AFY71" s="33"/>
-      <c r="AFZ71" s="33"/>
-      <c r="AGA71" s="33"/>
-      <c r="AGB71" s="33"/>
-      <c r="AGC71" s="33"/>
-      <c r="AGD71" s="33"/>
-      <c r="AGE71" s="33"/>
-      <c r="AGF71" s="33"/>
-      <c r="AGG71" s="33"/>
-      <c r="AGH71" s="33"/>
-      <c r="AGI71" s="33"/>
-      <c r="AGJ71" s="33"/>
-      <c r="AGK71" s="33"/>
-      <c r="AGL71" s="33"/>
-      <c r="AGM71" s="33"/>
-      <c r="AGN71" s="33"/>
-      <c r="AGO71" s="33"/>
-      <c r="AGP71" s="33"/>
-      <c r="AGQ71" s="33"/>
-      <c r="AGR71" s="33"/>
-      <c r="AGS71" s="33"/>
-      <c r="AGT71" s="33"/>
-      <c r="AGU71" s="33"/>
-      <c r="AGV71" s="33"/>
-      <c r="AGW71" s="33"/>
-      <c r="AGX71" s="33"/>
-      <c r="AGY71" s="33"/>
-      <c r="AGZ71" s="33"/>
-      <c r="AHA71" s="33"/>
-      <c r="AHB71" s="33"/>
-      <c r="AHC71" s="33"/>
-      <c r="AHD71" s="33"/>
-      <c r="AHE71" s="33"/>
-      <c r="AHF71" s="33"/>
-      <c r="AHG71" s="33"/>
-      <c r="AHH71" s="33"/>
-      <c r="AHI71" s="33"/>
-      <c r="AHJ71" s="33"/>
-      <c r="AHK71" s="33"/>
-      <c r="AHL71" s="33"/>
-      <c r="AHM71" s="33"/>
-      <c r="AHN71" s="33"/>
-      <c r="AHO71" s="33"/>
-      <c r="AHP71" s="33"/>
-      <c r="AHQ71" s="33"/>
-      <c r="AHR71" s="33"/>
-      <c r="AHS71" s="33"/>
-      <c r="AHT71" s="33"/>
-      <c r="AHU71" s="33"/>
-      <c r="AHV71" s="33"/>
-      <c r="AHW71" s="33"/>
-      <c r="AHX71" s="33"/>
-      <c r="AHY71" s="33"/>
-      <c r="AHZ71" s="33"/>
-      <c r="AIA71" s="33"/>
-      <c r="AIB71" s="33"/>
-      <c r="AIC71" s="33"/>
-      <c r="AID71" s="33"/>
-      <c r="AIE71" s="33"/>
-      <c r="AIF71" s="33"/>
-      <c r="AIG71" s="33"/>
-      <c r="AIH71" s="33"/>
-      <c r="AII71" s="33"/>
-      <c r="AIJ71" s="33"/>
-      <c r="AIK71" s="33"/>
-      <c r="AIL71" s="33"/>
-      <c r="AIM71" s="33"/>
-      <c r="AIN71" s="33"/>
-      <c r="AIO71" s="33"/>
-      <c r="AIP71" s="33"/>
-      <c r="AIQ71" s="33"/>
-      <c r="AIR71" s="33"/>
-      <c r="AIS71" s="33"/>
-      <c r="AIT71" s="33"/>
-      <c r="AIU71" s="33"/>
-      <c r="AIV71" s="33"/>
-      <c r="AIW71" s="33"/>
-      <c r="AIX71" s="33"/>
-      <c r="AIY71" s="33"/>
-      <c r="AIZ71" s="33"/>
-      <c r="AJA71" s="33"/>
-      <c r="AJB71" s="33"/>
-      <c r="AJC71" s="33"/>
-      <c r="AJD71" s="33"/>
-      <c r="AJE71" s="33"/>
-      <c r="AJF71" s="33"/>
-      <c r="AJG71" s="33"/>
-      <c r="AJH71" s="33"/>
-      <c r="AJI71" s="33"/>
-      <c r="AJJ71" s="33"/>
-      <c r="AJK71" s="33"/>
-      <c r="AJL71" s="33"/>
-      <c r="AJM71" s="33"/>
-      <c r="AJN71" s="33"/>
-      <c r="AJO71" s="33"/>
-      <c r="AJP71" s="33"/>
-      <c r="AJQ71" s="33"/>
-      <c r="AJR71" s="33"/>
-      <c r="AJS71" s="33"/>
-      <c r="AJT71" s="33"/>
-      <c r="AJU71" s="33"/>
-      <c r="AJV71" s="33"/>
-      <c r="AJW71" s="33"/>
-      <c r="AJX71" s="33"/>
-      <c r="AJY71" s="33"/>
-      <c r="AJZ71" s="33"/>
-      <c r="AKA71" s="33"/>
-      <c r="AKB71" s="33"/>
-      <c r="AKC71" s="33"/>
-      <c r="AKD71" s="33"/>
-      <c r="AKE71" s="33"/>
-      <c r="AKF71" s="33"/>
-      <c r="AKG71" s="33"/>
-      <c r="AKH71" s="33"/>
-      <c r="AKI71" s="33"/>
-      <c r="AKJ71" s="33"/>
-      <c r="AKK71" s="33"/>
-      <c r="AKL71" s="33"/>
-      <c r="AKM71" s="33"/>
-      <c r="AKN71" s="33"/>
-      <c r="AKO71" s="33"/>
-      <c r="AKP71" s="33"/>
-      <c r="AKQ71" s="33"/>
-      <c r="AKR71" s="33"/>
-      <c r="AKS71" s="33"/>
-      <c r="AKT71" s="33"/>
-      <c r="AKU71" s="33"/>
-      <c r="AKV71" s="33"/>
-      <c r="AKW71" s="33"/>
-      <c r="AKX71" s="33"/>
-      <c r="AKY71" s="33"/>
-      <c r="AKZ71" s="33"/>
-      <c r="ALA71" s="33"/>
-      <c r="ALB71" s="33"/>
-      <c r="ALC71" s="33"/>
-      <c r="ALD71" s="33"/>
-      <c r="ALE71" s="33"/>
-      <c r="ALF71" s="33"/>
-      <c r="ALG71" s="33"/>
-      <c r="ALH71" s="33"/>
-      <c r="ALI71" s="33"/>
-      <c r="ALJ71" s="33"/>
-      <c r="ALK71" s="33"/>
-      <c r="ALL71" s="33"/>
-      <c r="ALM71" s="33"/>
-      <c r="ALN71" s="33"/>
-      <c r="ALO71" s="33"/>
-      <c r="ALP71" s="33"/>
-      <c r="ALQ71" s="33"/>
-      <c r="ALR71" s="33"/>
-      <c r="ALS71" s="33"/>
-      <c r="ALT71" s="33"/>
-      <c r="ALU71" s="33"/>
-      <c r="ALV71" s="33"/>
-      <c r="ALW71" s="33"/>
-      <c r="ALX71" s="33"/>
-      <c r="ALY71" s="33"/>
-      <c r="ALZ71" s="33"/>
-      <c r="AMA71" s="33"/>
-      <c r="AMB71" s="33"/>
-      <c r="AMC71" s="33"/>
-      <c r="AMD71" s="33"/>
-      <c r="AME71" s="33"/>
-      <c r="AMF71" s="33"/>
-      <c r="AMG71" s="33"/>
-      <c r="AMH71" s="33"/>
-      <c r="AMI71" s="33"/>
-      <c r="AMJ71" s="33"/>
-      <c r="AMK71" s="33"/>
+      <c r="A71" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B71" s="26"/>
+      <c r="C71" s="27"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="27"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="27"/>
+      <c r="N71" s="26"/>
+      <c r="O71" s="27"/>
+      <c r="P71" s="28"/>
+      <c r="Q71" s="26"/>
+      <c r="R71" s="27"/>
+      <c r="S71" s="26"/>
+      <c r="T71" s="27"/>
+      <c r="U71" s="26"/>
+      <c r="V71" s="26"/>
+      <c r="W71" s="27"/>
+      <c r="X71" s="26"/>
+      <c r="Y71" s="27"/>
+      <c r="Z71" s="26"/>
+      <c r="AA71" s="27"/>
+      <c r="AB71" s="28"/>
+      <c r="AC71" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD71" s="27"/>
+      <c r="AE71" s="26"/>
+      <c r="AF71" s="27"/>
+      <c r="AG71" s="26"/>
+      <c r="AH71" s="26"/>
+      <c r="AI71" s="27"/>
+      <c r="AJ71" s="25"/>
+      <c r="AK71" s="27"/>
+      <c r="AL71" s="26"/>
+      <c r="AM71" s="27"/>
+      <c r="AN71" s="28"/>
+      <c r="AO71" s="25"/>
+      <c r="AP71" s="27"/>
+      <c r="AQ71" s="26"/>
+      <c r="AR71" s="27"/>
+      <c r="AS71" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT71" s="26"/>
+      <c r="AU71" s="27"/>
+      <c r="AV71" s="26"/>
+      <c r="AW71" s="27"/>
+      <c r="AX71" s="26"/>
+      <c r="AY71" s="27"/>
+      <c r="AZ71" s="28"/>
+      <c r="BA71" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB71" s="27"/>
+      <c r="BC71" s="26"/>
+      <c r="BD71" s="27"/>
+      <c r="BE71" s="26"/>
+      <c r="BF71" s="26"/>
+      <c r="BG71" s="27"/>
+      <c r="BH71" s="26"/>
+      <c r="BI71" s="27"/>
+      <c r="BJ71" s="26"/>
+      <c r="BK71" s="27"/>
+      <c r="BL71" s="28"/>
+      <c r="BM71" s="26"/>
+      <c r="BN71" s="27"/>
+      <c r="BO71" s="26"/>
+      <c r="BP71" s="27"/>
+      <c r="BQ71" s="26"/>
+      <c r="BR71" s="26"/>
+      <c r="BS71" s="27"/>
+      <c r="BT71" s="26"/>
+      <c r="BU71" s="27"/>
+      <c r="BV71" s="26"/>
+      <c r="BW71" s="27"/>
+      <c r="BX71" s="28"/>
+      <c r="BY71" s="26"/>
+      <c r="BZ71" s="27"/>
+      <c r="CA71" s="26"/>
+      <c r="CB71" s="27"/>
+      <c r="CC71" s="26"/>
+      <c r="CD71" s="26"/>
+      <c r="CE71" s="27"/>
+      <c r="CF71" s="26"/>
+      <c r="CG71" s="27"/>
+      <c r="CH71" s="26"/>
+      <c r="CI71" s="27"/>
+      <c r="CJ71" s="28"/>
+      <c r="CK71" s="26"/>
+      <c r="CL71" s="31"/>
+      <c r="CM71" s="31"/>
+      <c r="CN71" s="31"/>
+      <c r="CO71" s="31"/>
+      <c r="CP71" s="31"/>
+      <c r="CQ71" s="31"/>
+      <c r="CR71" s="31"/>
+      <c r="CS71" s="31"/>
+      <c r="CT71" s="31"/>
+      <c r="CU71" s="31"/>
+      <c r="CV71" s="31"/>
+      <c r="CW71" s="31"/>
+      <c r="CX71" s="31"/>
+      <c r="CY71" s="31"/>
+      <c r="CZ71" s="31"/>
+      <c r="DA71" s="31"/>
+      <c r="DB71" s="31"/>
+      <c r="DC71" s="31"/>
+      <c r="DD71" s="31"/>
+      <c r="DE71" s="31"/>
+      <c r="DF71" s="31"/>
+      <c r="DG71" s="31"/>
+      <c r="DH71" s="31"/>
+      <c r="DI71" s="31"/>
+      <c r="DJ71" s="31"/>
+      <c r="DK71" s="31"/>
+      <c r="DL71" s="31"/>
+      <c r="DM71" s="31"/>
+      <c r="DN71" s="31"/>
+      <c r="DO71" s="31"/>
+      <c r="DP71" s="31"/>
+      <c r="DQ71" s="31"/>
+      <c r="DR71" s="31"/>
+      <c r="DS71" s="31"/>
+      <c r="DT71" s="31"/>
+      <c r="DU71" s="31"/>
+      <c r="DV71" s="31"/>
+      <c r="DW71" s="31"/>
+      <c r="DX71" s="31"/>
+      <c r="DY71" s="31"/>
+      <c r="DZ71" s="31"/>
+      <c r="EA71" s="31"/>
+      <c r="EB71" s="31"/>
+      <c r="EC71" s="31"/>
+      <c r="ED71" s="31"/>
+      <c r="EE71" s="31"/>
+      <c r="EF71" s="31"/>
+      <c r="EG71" s="31"/>
+      <c r="EH71" s="31"/>
+      <c r="EI71" s="31"/>
+      <c r="EJ71" s="31"/>
+      <c r="EK71" s="31"/>
+      <c r="EL71" s="31"/>
+      <c r="EM71" s="31"/>
+      <c r="EN71" s="31"/>
+      <c r="EO71" s="31"/>
+      <c r="EP71" s="31"/>
+      <c r="EQ71" s="31"/>
+      <c r="ER71" s="31"/>
+      <c r="ES71" s="31"/>
+      <c r="ET71" s="31"/>
+      <c r="EU71" s="31"/>
+      <c r="EV71" s="31"/>
+      <c r="EW71" s="31"/>
+      <c r="EX71" s="31"/>
+      <c r="EY71" s="31"/>
+      <c r="EZ71" s="31"/>
+      <c r="FA71" s="31"/>
+      <c r="FB71" s="31"/>
+      <c r="FC71" s="31"/>
+      <c r="FD71" s="31"/>
+      <c r="FE71" s="31"/>
+      <c r="FF71" s="31"/>
+      <c r="FG71" s="31"/>
+      <c r="FH71" s="31"/>
+      <c r="FI71" s="31"/>
+      <c r="FJ71" s="31"/>
+      <c r="FK71" s="31"/>
+      <c r="FL71" s="31"/>
+      <c r="FM71" s="31"/>
+      <c r="FN71" s="31"/>
+      <c r="FO71" s="31"/>
+      <c r="FP71" s="31"/>
+      <c r="FQ71" s="31"/>
+      <c r="FR71" s="31"/>
+      <c r="FS71" s="31"/>
+      <c r="FT71" s="31"/>
+      <c r="FU71" s="31"/>
+      <c r="FV71" s="31"/>
+      <c r="FW71" s="31"/>
+      <c r="FX71" s="31"/>
+      <c r="FY71" s="31"/>
+      <c r="FZ71" s="31"/>
+      <c r="GA71" s="31"/>
+      <c r="GB71" s="31"/>
+      <c r="GC71" s="31"/>
+      <c r="GD71" s="31"/>
+      <c r="GE71" s="31"/>
+      <c r="GF71" s="31"/>
+      <c r="GG71" s="31"/>
+      <c r="GH71" s="31"/>
+      <c r="GI71" s="31"/>
+      <c r="GJ71" s="31"/>
+      <c r="GK71" s="31"/>
+      <c r="GL71" s="31"/>
+      <c r="GM71" s="31"/>
+      <c r="GN71" s="31"/>
+      <c r="GO71" s="31"/>
+      <c r="GP71" s="31"/>
+      <c r="GQ71" s="31"/>
+      <c r="GR71" s="31"/>
+      <c r="GS71" s="31"/>
+      <c r="GT71" s="31"/>
+      <c r="GU71" s="31"/>
+      <c r="GV71" s="31"/>
+      <c r="GW71" s="31"/>
+      <c r="GX71" s="31"/>
+      <c r="GY71" s="31"/>
+      <c r="GZ71" s="31"/>
+      <c r="HA71" s="31"/>
+      <c r="HB71" s="31"/>
+      <c r="HC71" s="31"/>
+      <c r="HD71" s="31"/>
+      <c r="HE71" s="31"/>
+      <c r="HF71" s="31"/>
+      <c r="HG71" s="31"/>
+      <c r="HH71" s="31"/>
+      <c r="HI71" s="31"/>
+      <c r="HJ71" s="31"/>
+      <c r="HK71" s="31"/>
+      <c r="HL71" s="31"/>
+      <c r="HM71" s="31"/>
+      <c r="HN71" s="31"/>
+      <c r="HO71" s="31"/>
+      <c r="HP71" s="31"/>
+      <c r="HQ71" s="31"/>
+      <c r="HR71" s="31"/>
+      <c r="HS71" s="31"/>
+      <c r="HT71" s="31"/>
+      <c r="HU71" s="31"/>
+      <c r="HV71" s="31"/>
+      <c r="HW71" s="31"/>
+      <c r="HX71" s="31"/>
+      <c r="HY71" s="31"/>
+      <c r="HZ71" s="31"/>
+      <c r="IA71" s="31"/>
+      <c r="IB71" s="31"/>
+      <c r="IC71" s="31"/>
+      <c r="ID71" s="31"/>
+      <c r="IE71" s="31"/>
+      <c r="IF71" s="31"/>
+      <c r="IG71" s="31"/>
+      <c r="IH71" s="31"/>
+      <c r="II71" s="31"/>
+      <c r="IJ71" s="31"/>
+      <c r="IK71" s="31"/>
+      <c r="IL71" s="31"/>
+      <c r="IM71" s="31"/>
+      <c r="IN71" s="31"/>
+      <c r="IO71" s="31"/>
+      <c r="IP71" s="31"/>
+      <c r="IQ71" s="31"/>
+      <c r="IR71" s="31"/>
+      <c r="IS71" s="31"/>
+      <c r="IT71" s="31"/>
+      <c r="IU71" s="31"/>
+      <c r="IV71" s="31"/>
+      <c r="IW71" s="31"/>
+      <c r="IX71" s="31"/>
+      <c r="IY71" s="31"/>
+      <c r="IZ71" s="31"/>
+      <c r="JA71" s="31"/>
+      <c r="JB71" s="31"/>
+      <c r="JC71" s="31"/>
+      <c r="JD71" s="31"/>
+      <c r="JE71" s="31"/>
+      <c r="JF71" s="31"/>
+      <c r="JG71" s="31"/>
+      <c r="JH71" s="31"/>
+      <c r="JI71" s="31"/>
+      <c r="JJ71" s="31"/>
+      <c r="JK71" s="31"/>
+      <c r="JL71" s="31"/>
+      <c r="JM71" s="31"/>
+      <c r="JN71" s="31"/>
+      <c r="JO71" s="31"/>
+      <c r="JP71" s="31"/>
+      <c r="JQ71" s="31"/>
+      <c r="JR71" s="31"/>
+      <c r="JS71" s="31"/>
+      <c r="JT71" s="31"/>
+      <c r="JU71" s="31"/>
+      <c r="JV71" s="31"/>
+      <c r="JW71" s="31"/>
+      <c r="JX71" s="31"/>
+      <c r="JY71" s="31"/>
+      <c r="JZ71" s="31"/>
+      <c r="KA71" s="31"/>
+      <c r="KB71" s="31"/>
+      <c r="KC71" s="31"/>
+      <c r="KD71" s="31"/>
+      <c r="KE71" s="31"/>
+      <c r="KF71" s="31"/>
+      <c r="KG71" s="31"/>
+      <c r="KH71" s="31"/>
+      <c r="KI71" s="31"/>
+      <c r="KJ71" s="31"/>
+      <c r="KK71" s="31"/>
+      <c r="KL71" s="31"/>
+      <c r="KM71" s="31"/>
+      <c r="KN71" s="31"/>
+      <c r="KO71" s="31"/>
+      <c r="KP71" s="31"/>
+      <c r="KQ71" s="31"/>
+      <c r="KR71" s="31"/>
+      <c r="KS71" s="31"/>
+      <c r="KT71" s="31"/>
+      <c r="KU71" s="31"/>
+      <c r="KV71" s="31"/>
+      <c r="KW71" s="31"/>
+      <c r="KX71" s="31"/>
+      <c r="KY71" s="31"/>
+      <c r="KZ71" s="31"/>
+      <c r="LA71" s="31"/>
+      <c r="LB71" s="31"/>
+      <c r="LC71" s="31"/>
+      <c r="LD71" s="31"/>
+      <c r="LE71" s="31"/>
+      <c r="LF71" s="31"/>
+      <c r="LG71" s="31"/>
+      <c r="LH71" s="31"/>
+      <c r="LI71" s="31"/>
+      <c r="LJ71" s="31"/>
+      <c r="LK71" s="31"/>
+      <c r="LL71" s="31"/>
+      <c r="LM71" s="31"/>
+      <c r="LN71" s="31"/>
+      <c r="LO71" s="31"/>
+      <c r="LP71" s="31"/>
+      <c r="LQ71" s="31"/>
+      <c r="LR71" s="31"/>
+      <c r="LS71" s="31"/>
+      <c r="LT71" s="31"/>
+      <c r="LU71" s="31"/>
+      <c r="LV71" s="31"/>
+      <c r="LW71" s="31"/>
+      <c r="LX71" s="31"/>
+      <c r="LY71" s="31"/>
+      <c r="LZ71" s="31"/>
+      <c r="MA71" s="31"/>
+      <c r="MB71" s="31"/>
+      <c r="MC71" s="31"/>
+      <c r="MD71" s="31"/>
+      <c r="ME71" s="31"/>
+      <c r="MF71" s="31"/>
+      <c r="MG71" s="31"/>
+      <c r="MH71" s="31"/>
+      <c r="MI71" s="31"/>
+      <c r="MJ71" s="31"/>
+      <c r="MK71" s="31"/>
+      <c r="ML71" s="31"/>
+      <c r="MM71" s="31"/>
+      <c r="MN71" s="31"/>
+      <c r="MO71" s="31"/>
+      <c r="MP71" s="31"/>
+      <c r="MQ71" s="31"/>
+      <c r="MR71" s="31"/>
+      <c r="MS71" s="31"/>
+      <c r="MT71" s="31"/>
+      <c r="MU71" s="31"/>
+      <c r="MV71" s="31"/>
+      <c r="MW71" s="31"/>
+      <c r="MX71" s="31"/>
+      <c r="MY71" s="31"/>
+      <c r="MZ71" s="31"/>
+      <c r="NA71" s="31"/>
+      <c r="NB71" s="31"/>
+      <c r="NC71" s="31"/>
+      <c r="ND71" s="31"/>
+      <c r="NE71" s="31"/>
+      <c r="NF71" s="31"/>
+      <c r="NG71" s="31"/>
+      <c r="NH71" s="31"/>
+      <c r="NI71" s="31"/>
+      <c r="NJ71" s="31"/>
+      <c r="NK71" s="31"/>
+      <c r="NL71" s="31"/>
+      <c r="NM71" s="31"/>
+      <c r="NN71" s="31"/>
+      <c r="NO71" s="31"/>
+      <c r="NP71" s="31"/>
+      <c r="NQ71" s="31"/>
+      <c r="NR71" s="31"/>
+      <c r="NS71" s="31"/>
+      <c r="NT71" s="31"/>
+      <c r="NU71" s="31"/>
+      <c r="NV71" s="31"/>
+      <c r="NW71" s="31"/>
+      <c r="NX71" s="31"/>
+      <c r="NY71" s="31"/>
+      <c r="NZ71" s="31"/>
+      <c r="OA71" s="31"/>
+      <c r="OB71" s="31"/>
+      <c r="OC71" s="31"/>
+      <c r="OD71" s="31"/>
+      <c r="OE71" s="31"/>
+      <c r="OF71" s="31"/>
+      <c r="OG71" s="31"/>
+      <c r="OH71" s="31"/>
+      <c r="OI71" s="31"/>
+      <c r="OJ71" s="31"/>
+      <c r="OK71" s="31"/>
+      <c r="OL71" s="31"/>
+      <c r="OM71" s="31"/>
+      <c r="ON71" s="31"/>
+      <c r="OO71" s="31"/>
+      <c r="OP71" s="31"/>
+      <c r="OQ71" s="31"/>
+      <c r="OR71" s="31"/>
+      <c r="OS71" s="31"/>
+      <c r="OT71" s="31"/>
+      <c r="OU71" s="31"/>
+      <c r="OV71" s="31"/>
+      <c r="OW71" s="31"/>
+      <c r="OX71" s="31"/>
+      <c r="OY71" s="31"/>
+      <c r="OZ71" s="31"/>
+      <c r="PA71" s="31"/>
+      <c r="PB71" s="31"/>
+      <c r="PC71" s="31"/>
+      <c r="PD71" s="31"/>
+      <c r="PE71" s="31"/>
+      <c r="PF71" s="31"/>
+      <c r="PG71" s="31"/>
+      <c r="PH71" s="31"/>
+      <c r="PI71" s="31"/>
+      <c r="PJ71" s="31"/>
+      <c r="PK71" s="31"/>
+      <c r="PL71" s="31"/>
+      <c r="PM71" s="31"/>
+      <c r="PN71" s="31"/>
+      <c r="PO71" s="31"/>
+      <c r="PP71" s="31"/>
+      <c r="PQ71" s="31"/>
+      <c r="PR71" s="31"/>
+      <c r="PS71" s="31"/>
+      <c r="PT71" s="31"/>
+      <c r="PU71" s="31"/>
+      <c r="PV71" s="31"/>
+      <c r="PW71" s="31"/>
+      <c r="PX71" s="31"/>
+      <c r="PY71" s="31"/>
+      <c r="PZ71" s="31"/>
+      <c r="QA71" s="31"/>
+      <c r="QB71" s="31"/>
+      <c r="QC71" s="31"/>
+      <c r="QD71" s="31"/>
+      <c r="QE71" s="31"/>
+      <c r="QF71" s="31"/>
+      <c r="QG71" s="31"/>
+      <c r="QH71" s="31"/>
+      <c r="QI71" s="31"/>
+      <c r="QJ71" s="31"/>
+      <c r="QK71" s="31"/>
+      <c r="QL71" s="31"/>
+      <c r="QM71" s="31"/>
+      <c r="QN71" s="31"/>
+      <c r="QO71" s="31"/>
+      <c r="QP71" s="31"/>
+      <c r="QQ71" s="31"/>
+      <c r="QR71" s="31"/>
+      <c r="QS71" s="31"/>
+      <c r="QT71" s="31"/>
+      <c r="QU71" s="31"/>
+      <c r="QV71" s="31"/>
+      <c r="QW71" s="31"/>
+      <c r="QX71" s="31"/>
+      <c r="QY71" s="31"/>
+      <c r="QZ71" s="31"/>
+      <c r="RA71" s="31"/>
+      <c r="RB71" s="31"/>
+      <c r="RC71" s="31"/>
+      <c r="RD71" s="31"/>
+      <c r="RE71" s="31"/>
+      <c r="RF71" s="31"/>
+      <c r="RG71" s="31"/>
+      <c r="RH71" s="31"/>
+      <c r="RI71" s="31"/>
+      <c r="RJ71" s="31"/>
+      <c r="RK71" s="31"/>
+      <c r="RL71" s="31"/>
+      <c r="RM71" s="31"/>
+      <c r="RN71" s="31"/>
+      <c r="RO71" s="31"/>
+      <c r="RP71" s="31"/>
+      <c r="RQ71" s="31"/>
+      <c r="RR71" s="31"/>
+      <c r="RS71" s="31"/>
+      <c r="RT71" s="31"/>
+      <c r="RU71" s="31"/>
+      <c r="RV71" s="31"/>
+      <c r="RW71" s="31"/>
+      <c r="RX71" s="31"/>
+      <c r="RY71" s="31"/>
+      <c r="RZ71" s="31"/>
+      <c r="SA71" s="31"/>
+      <c r="SB71" s="31"/>
+      <c r="SC71" s="31"/>
+      <c r="SD71" s="31"/>
+      <c r="SE71" s="31"/>
+      <c r="SF71" s="31"/>
+      <c r="SG71" s="31"/>
+      <c r="SH71" s="31"/>
+      <c r="SI71" s="31"/>
+      <c r="SJ71" s="31"/>
+      <c r="SK71" s="31"/>
+      <c r="SL71" s="31"/>
+      <c r="SM71" s="31"/>
+      <c r="SN71" s="31"/>
+      <c r="SO71" s="31"/>
+      <c r="SP71" s="31"/>
+      <c r="SQ71" s="31"/>
+      <c r="SR71" s="31"/>
+      <c r="SS71" s="31"/>
+      <c r="ST71" s="31"/>
+      <c r="SU71" s="31"/>
+      <c r="SV71" s="31"/>
+      <c r="SW71" s="31"/>
+      <c r="SX71" s="31"/>
+      <c r="SY71" s="31"/>
+      <c r="SZ71" s="31"/>
+      <c r="TA71" s="31"/>
+      <c r="TB71" s="31"/>
+      <c r="TC71" s="31"/>
+      <c r="TD71" s="31"/>
+      <c r="TE71" s="31"/>
+      <c r="TF71" s="31"/>
+      <c r="TG71" s="31"/>
+      <c r="TH71" s="31"/>
+      <c r="TI71" s="31"/>
+      <c r="TJ71" s="31"/>
+      <c r="TK71" s="31"/>
+      <c r="TL71" s="31"/>
+      <c r="TM71" s="31"/>
+      <c r="TN71" s="31"/>
+      <c r="TO71" s="31"/>
+      <c r="TP71" s="31"/>
+      <c r="TQ71" s="31"/>
+      <c r="TR71" s="31"/>
+      <c r="TS71" s="31"/>
+      <c r="TT71" s="31"/>
+      <c r="TU71" s="31"/>
+      <c r="TV71" s="31"/>
+      <c r="TW71" s="31"/>
+      <c r="TX71" s="31"/>
+      <c r="TY71" s="31"/>
+      <c r="TZ71" s="31"/>
+      <c r="UA71" s="31"/>
+      <c r="UB71" s="31"/>
+      <c r="UC71" s="31"/>
+      <c r="UD71" s="31"/>
+      <c r="UE71" s="31"/>
+      <c r="UF71" s="31"/>
+      <c r="UG71" s="31"/>
+      <c r="UH71" s="31"/>
+      <c r="UI71" s="31"/>
+      <c r="UJ71" s="31"/>
+      <c r="UK71" s="31"/>
+      <c r="UL71" s="31"/>
+      <c r="UM71" s="31"/>
+      <c r="UN71" s="31"/>
+      <c r="UO71" s="31"/>
+      <c r="UP71" s="31"/>
+      <c r="UQ71" s="31"/>
+      <c r="UR71" s="31"/>
+      <c r="US71" s="31"/>
+      <c r="UT71" s="31"/>
+      <c r="UU71" s="31"/>
+      <c r="UV71" s="31"/>
+      <c r="UW71" s="31"/>
+      <c r="UX71" s="31"/>
+      <c r="UY71" s="31"/>
+      <c r="UZ71" s="31"/>
+      <c r="VA71" s="31"/>
+      <c r="VB71" s="31"/>
+      <c r="VC71" s="31"/>
+      <c r="VD71" s="31"/>
+      <c r="VE71" s="31"/>
+      <c r="VF71" s="31"/>
+      <c r="VG71" s="31"/>
+      <c r="VH71" s="31"/>
+      <c r="VI71" s="31"/>
+      <c r="VJ71" s="31"/>
+      <c r="VK71" s="31"/>
+      <c r="VL71" s="31"/>
+      <c r="VM71" s="31"/>
+      <c r="VN71" s="31"/>
+      <c r="VO71" s="31"/>
+      <c r="VP71" s="31"/>
+      <c r="VQ71" s="31"/>
+      <c r="VR71" s="31"/>
+      <c r="VS71" s="31"/>
+      <c r="VT71" s="31"/>
+      <c r="VU71" s="31"/>
+      <c r="VV71" s="31"/>
+      <c r="VW71" s="31"/>
+      <c r="VX71" s="31"/>
+      <c r="VY71" s="31"/>
+      <c r="VZ71" s="31"/>
+      <c r="WA71" s="31"/>
+      <c r="WB71" s="31"/>
+      <c r="WC71" s="31"/>
+      <c r="WD71" s="31"/>
+      <c r="WE71" s="31"/>
+      <c r="WF71" s="31"/>
+      <c r="WG71" s="31"/>
+      <c r="WH71" s="31"/>
+      <c r="WI71" s="31"/>
+      <c r="WJ71" s="31"/>
+      <c r="WK71" s="31"/>
+      <c r="WL71" s="31"/>
+      <c r="WM71" s="31"/>
+      <c r="WN71" s="31"/>
+      <c r="WO71" s="31"/>
+      <c r="WP71" s="31"/>
+      <c r="WQ71" s="31"/>
+      <c r="WR71" s="31"/>
+      <c r="WS71" s="31"/>
+      <c r="WT71" s="31"/>
+      <c r="WU71" s="31"/>
+      <c r="WV71" s="31"/>
+      <c r="WW71" s="31"/>
+      <c r="WX71" s="31"/>
+      <c r="WY71" s="31"/>
+      <c r="WZ71" s="31"/>
+      <c r="XA71" s="31"/>
+      <c r="XB71" s="31"/>
+      <c r="XC71" s="31"/>
+      <c r="XD71" s="31"/>
+      <c r="XE71" s="31"/>
+      <c r="XF71" s="31"/>
+      <c r="XG71" s="31"/>
+      <c r="XH71" s="31"/>
+      <c r="XI71" s="31"/>
+      <c r="XJ71" s="31"/>
+      <c r="XK71" s="31"/>
+      <c r="XL71" s="31"/>
+      <c r="XM71" s="31"/>
+      <c r="XN71" s="31"/>
+      <c r="XO71" s="31"/>
+      <c r="XP71" s="31"/>
+      <c r="XQ71" s="31"/>
+      <c r="XR71" s="31"/>
+      <c r="XS71" s="31"/>
+      <c r="XT71" s="31"/>
+      <c r="XU71" s="31"/>
+      <c r="XV71" s="31"/>
+      <c r="XW71" s="31"/>
+      <c r="XX71" s="31"/>
+      <c r="XY71" s="31"/>
+      <c r="XZ71" s="31"/>
+      <c r="YA71" s="31"/>
+      <c r="YB71" s="31"/>
+      <c r="YC71" s="31"/>
+      <c r="YD71" s="31"/>
+      <c r="YE71" s="31"/>
+      <c r="YF71" s="31"/>
+      <c r="YG71" s="31"/>
+      <c r="YH71" s="31"/>
+      <c r="YI71" s="31"/>
+      <c r="YJ71" s="31"/>
+      <c r="YK71" s="31"/>
+      <c r="YL71" s="31"/>
+      <c r="YM71" s="31"/>
+      <c r="YN71" s="31"/>
+      <c r="YO71" s="31"/>
+      <c r="YP71" s="31"/>
+      <c r="YQ71" s="31"/>
+      <c r="YR71" s="31"/>
+      <c r="YS71" s="31"/>
+      <c r="YT71" s="31"/>
+      <c r="YU71" s="31"/>
+      <c r="YV71" s="31"/>
+      <c r="YW71" s="31"/>
+      <c r="YX71" s="31"/>
+      <c r="YY71" s="31"/>
+      <c r="YZ71" s="31"/>
+      <c r="ZA71" s="31"/>
+      <c r="ZB71" s="31"/>
+      <c r="ZC71" s="31"/>
+      <c r="ZD71" s="31"/>
+      <c r="ZE71" s="31"/>
+      <c r="ZF71" s="31"/>
+      <c r="ZG71" s="31"/>
+      <c r="ZH71" s="31"/>
+      <c r="ZI71" s="31"/>
+      <c r="ZJ71" s="31"/>
+      <c r="ZK71" s="31"/>
+      <c r="ZL71" s="31"/>
+      <c r="ZM71" s="31"/>
+      <c r="ZN71" s="31"/>
+      <c r="ZO71" s="31"/>
+      <c r="ZP71" s="31"/>
+      <c r="ZQ71" s="31"/>
+      <c r="ZR71" s="31"/>
+      <c r="ZS71" s="31"/>
+      <c r="ZT71" s="31"/>
+      <c r="ZU71" s="31"/>
+      <c r="ZV71" s="31"/>
+      <c r="ZW71" s="31"/>
+      <c r="ZX71" s="31"/>
+      <c r="ZY71" s="31"/>
+      <c r="ZZ71" s="31"/>
+      <c r="AAA71" s="31"/>
+      <c r="AAB71" s="31"/>
+      <c r="AAC71" s="31"/>
+      <c r="AAD71" s="31"/>
+      <c r="AAE71" s="31"/>
+      <c r="AAF71" s="31"/>
+      <c r="AAG71" s="31"/>
+      <c r="AAH71" s="31"/>
+      <c r="AAI71" s="31"/>
+      <c r="AAJ71" s="31"/>
+      <c r="AAK71" s="31"/>
+      <c r="AAL71" s="31"/>
+      <c r="AAM71" s="31"/>
+      <c r="AAN71" s="31"/>
+      <c r="AAO71" s="31"/>
+      <c r="AAP71" s="31"/>
+      <c r="AAQ71" s="31"/>
+      <c r="AAR71" s="31"/>
+      <c r="AAS71" s="31"/>
+      <c r="AAT71" s="31"/>
+      <c r="AAU71" s="31"/>
+      <c r="AAV71" s="31"/>
+      <c r="AAW71" s="31"/>
+      <c r="AAX71" s="31"/>
+      <c r="AAY71" s="31"/>
+      <c r="AAZ71" s="31"/>
+      <c r="ABA71" s="31"/>
+      <c r="ABB71" s="31"/>
+      <c r="ABC71" s="31"/>
+      <c r="ABD71" s="31"/>
+      <c r="ABE71" s="31"/>
+      <c r="ABF71" s="31"/>
+      <c r="ABG71" s="31"/>
+      <c r="ABH71" s="31"/>
+      <c r="ABI71" s="31"/>
+      <c r="ABJ71" s="31"/>
+      <c r="ABK71" s="31"/>
+      <c r="ABL71" s="31"/>
+      <c r="ABM71" s="31"/>
+      <c r="ABN71" s="31"/>
+      <c r="ABO71" s="31"/>
+      <c r="ABP71" s="31"/>
+      <c r="ABQ71" s="31"/>
+      <c r="ABR71" s="31"/>
+      <c r="ABS71" s="31"/>
+      <c r="ABT71" s="31"/>
+      <c r="ABU71" s="31"/>
+      <c r="ABV71" s="31"/>
+      <c r="ABW71" s="31"/>
+      <c r="ABX71" s="31"/>
+      <c r="ABY71" s="31"/>
+      <c r="ABZ71" s="31"/>
+      <c r="ACA71" s="31"/>
+      <c r="ACB71" s="31"/>
+      <c r="ACC71" s="31"/>
+      <c r="ACD71" s="31"/>
+      <c r="ACE71" s="31"/>
+      <c r="ACF71" s="31"/>
+      <c r="ACG71" s="31"/>
+      <c r="ACH71" s="31"/>
+      <c r="ACI71" s="31"/>
+      <c r="ACJ71" s="31"/>
+      <c r="ACK71" s="31"/>
+      <c r="ACL71" s="31"/>
+      <c r="ACM71" s="31"/>
+      <c r="ACN71" s="31"/>
+      <c r="ACO71" s="31"/>
+      <c r="ACP71" s="31"/>
+      <c r="ACQ71" s="31"/>
+      <c r="ACR71" s="31"/>
+      <c r="ACS71" s="31"/>
+      <c r="ACT71" s="31"/>
+      <c r="ACU71" s="31"/>
+      <c r="ACV71" s="31"/>
+      <c r="ACW71" s="31"/>
+      <c r="ACX71" s="31"/>
+      <c r="ACY71" s="31"/>
+      <c r="ACZ71" s="31"/>
+      <c r="ADA71" s="31"/>
+      <c r="ADB71" s="31"/>
+      <c r="ADC71" s="31"/>
+      <c r="ADD71" s="31"/>
+      <c r="ADE71" s="31"/>
+      <c r="ADF71" s="31"/>
+      <c r="ADG71" s="31"/>
+      <c r="ADH71" s="31"/>
+      <c r="ADI71" s="31"/>
+      <c r="ADJ71" s="31"/>
+      <c r="ADK71" s="31"/>
+      <c r="ADL71" s="31"/>
+      <c r="ADM71" s="31"/>
+      <c r="ADN71" s="31"/>
+      <c r="ADO71" s="31"/>
+      <c r="ADP71" s="31"/>
+      <c r="ADQ71" s="31"/>
+      <c r="ADR71" s="31"/>
+      <c r="ADS71" s="31"/>
+      <c r="ADT71" s="31"/>
+      <c r="ADU71" s="31"/>
+      <c r="ADV71" s="31"/>
+      <c r="ADW71" s="31"/>
+      <c r="ADX71" s="31"/>
+      <c r="ADY71" s="31"/>
+      <c r="ADZ71" s="31"/>
+      <c r="AEA71" s="31"/>
+      <c r="AEB71" s="31"/>
+      <c r="AEC71" s="31"/>
+      <c r="AED71" s="31"/>
+      <c r="AEE71" s="31"/>
+      <c r="AEF71" s="31"/>
+      <c r="AEG71" s="31"/>
+      <c r="AEH71" s="31"/>
+      <c r="AEI71" s="31"/>
+      <c r="AEJ71" s="31"/>
+      <c r="AEK71" s="31"/>
+      <c r="AEL71" s="31"/>
+      <c r="AEM71" s="31"/>
+      <c r="AEN71" s="31"/>
+      <c r="AEO71" s="31"/>
+      <c r="AEP71" s="31"/>
+      <c r="AEQ71" s="31"/>
+      <c r="AER71" s="31"/>
+      <c r="AES71" s="31"/>
+      <c r="AET71" s="31"/>
+      <c r="AEU71" s="31"/>
+      <c r="AEV71" s="31"/>
+      <c r="AEW71" s="31"/>
+      <c r="AEX71" s="31"/>
+      <c r="AEY71" s="31"/>
+      <c r="AEZ71" s="31"/>
+      <c r="AFA71" s="31"/>
+      <c r="AFB71" s="31"/>
+      <c r="AFC71" s="31"/>
+      <c r="AFD71" s="31"/>
+      <c r="AFE71" s="31"/>
+      <c r="AFF71" s="31"/>
+      <c r="AFG71" s="31"/>
+      <c r="AFH71" s="31"/>
+      <c r="AFI71" s="31"/>
+      <c r="AFJ71" s="31"/>
+      <c r="AFK71" s="31"/>
+      <c r="AFL71" s="31"/>
+      <c r="AFM71" s="31"/>
+      <c r="AFN71" s="31"/>
+      <c r="AFO71" s="31"/>
+      <c r="AFP71" s="31"/>
+      <c r="AFQ71" s="31"/>
+      <c r="AFR71" s="31"/>
+      <c r="AFS71" s="31"/>
+      <c r="AFT71" s="31"/>
+      <c r="AFU71" s="31"/>
+      <c r="AFV71" s="31"/>
+      <c r="AFW71" s="31"/>
+      <c r="AFX71" s="31"/>
+      <c r="AFY71" s="31"/>
+      <c r="AFZ71" s="31"/>
+      <c r="AGA71" s="31"/>
+      <c r="AGB71" s="31"/>
+      <c r="AGC71" s="31"/>
+      <c r="AGD71" s="31"/>
+      <c r="AGE71" s="31"/>
+      <c r="AGF71" s="31"/>
+      <c r="AGG71" s="31"/>
+      <c r="AGH71" s="31"/>
+      <c r="AGI71" s="31"/>
+      <c r="AGJ71" s="31"/>
+      <c r="AGK71" s="31"/>
+      <c r="AGL71" s="31"/>
+      <c r="AGM71" s="31"/>
+      <c r="AGN71" s="31"/>
+      <c r="AGO71" s="31"/>
+      <c r="AGP71" s="31"/>
+      <c r="AGQ71" s="31"/>
+      <c r="AGR71" s="31"/>
+      <c r="AGS71" s="31"/>
+      <c r="AGT71" s="31"/>
+      <c r="AGU71" s="31"/>
+      <c r="AGV71" s="31"/>
+      <c r="AGW71" s="31"/>
+      <c r="AGX71" s="31"/>
+      <c r="AGY71" s="31"/>
+      <c r="AGZ71" s="31"/>
+      <c r="AHA71" s="31"/>
+      <c r="AHB71" s="31"/>
+      <c r="AHC71" s="31"/>
+      <c r="AHD71" s="31"/>
+      <c r="AHE71" s="31"/>
+      <c r="AHF71" s="31"/>
+      <c r="AHG71" s="31"/>
+      <c r="AHH71" s="31"/>
+      <c r="AHI71" s="31"/>
+      <c r="AHJ71" s="31"/>
+      <c r="AHK71" s="31"/>
+      <c r="AHL71" s="31"/>
+      <c r="AHM71" s="31"/>
+      <c r="AHN71" s="31"/>
+      <c r="AHO71" s="31"/>
+      <c r="AHP71" s="31"/>
+      <c r="AHQ71" s="31"/>
+      <c r="AHR71" s="31"/>
+      <c r="AHS71" s="31"/>
+      <c r="AHT71" s="31"/>
+      <c r="AHU71" s="31"/>
+      <c r="AHV71" s="31"/>
+      <c r="AHW71" s="31"/>
+      <c r="AHX71" s="31"/>
+      <c r="AHY71" s="31"/>
+      <c r="AHZ71" s="31"/>
+      <c r="AIA71" s="31"/>
+      <c r="AIB71" s="31"/>
+      <c r="AIC71" s="31"/>
+      <c r="AID71" s="31"/>
+      <c r="AIE71" s="31"/>
+      <c r="AIF71" s="31"/>
+      <c r="AIG71" s="31"/>
+      <c r="AIH71" s="31"/>
+      <c r="AII71" s="31"/>
+      <c r="AIJ71" s="31"/>
+      <c r="AIK71" s="31"/>
+      <c r="AIL71" s="31"/>
+      <c r="AIM71" s="31"/>
+      <c r="AIN71" s="31"/>
+      <c r="AIO71" s="31"/>
+      <c r="AIP71" s="31"/>
+      <c r="AIQ71" s="31"/>
+      <c r="AIR71" s="31"/>
+      <c r="AIS71" s="31"/>
+      <c r="AIT71" s="31"/>
+      <c r="AIU71" s="31"/>
+      <c r="AIV71" s="31"/>
+      <c r="AIW71" s="31"/>
+      <c r="AIX71" s="31"/>
+      <c r="AIY71" s="31"/>
+      <c r="AIZ71" s="31"/>
+      <c r="AJA71" s="31"/>
+      <c r="AJB71" s="31"/>
+      <c r="AJC71" s="31"/>
+      <c r="AJD71" s="31"/>
+      <c r="AJE71" s="31"/>
+      <c r="AJF71" s="31"/>
+      <c r="AJG71" s="31"/>
+      <c r="AJH71" s="31"/>
+      <c r="AJI71" s="31"/>
+      <c r="AJJ71" s="31"/>
+      <c r="AJK71" s="31"/>
+      <c r="AJL71" s="31"/>
+      <c r="AJM71" s="31"/>
+      <c r="AJN71" s="31"/>
+      <c r="AJO71" s="31"/>
+      <c r="AJP71" s="31"/>
+      <c r="AJQ71" s="31"/>
+      <c r="AJR71" s="31"/>
+      <c r="AJS71" s="31"/>
+      <c r="AJT71" s="31"/>
+      <c r="AJU71" s="31"/>
+      <c r="AJV71" s="31"/>
+      <c r="AJW71" s="31"/>
+      <c r="AJX71" s="31"/>
+      <c r="AJY71" s="31"/>
+      <c r="AJZ71" s="31"/>
+      <c r="AKA71" s="31"/>
+      <c r="AKB71" s="31"/>
+      <c r="AKC71" s="31"/>
+      <c r="AKD71" s="31"/>
+      <c r="AKE71" s="31"/>
+      <c r="AKF71" s="31"/>
+      <c r="AKG71" s="31"/>
+      <c r="AKH71" s="31"/>
+      <c r="AKI71" s="31"/>
+      <c r="AKJ71" s="31"/>
+      <c r="AKK71" s="31"/>
+      <c r="AKL71" s="31"/>
+      <c r="AKM71" s="31"/>
+      <c r="AKN71" s="31"/>
+      <c r="AKO71" s="31"/>
+      <c r="AKP71" s="31"/>
+      <c r="AKQ71" s="31"/>
+      <c r="AKR71" s="31"/>
+      <c r="AKS71" s="31"/>
+      <c r="AKT71" s="31"/>
+      <c r="AKU71" s="31"/>
+      <c r="AKV71" s="31"/>
+      <c r="AKW71" s="31"/>
+      <c r="AKX71" s="31"/>
+      <c r="AKY71" s="31"/>
+      <c r="AKZ71" s="31"/>
+      <c r="ALA71" s="31"/>
+      <c r="ALB71" s="31"/>
+      <c r="ALC71" s="31"/>
+      <c r="ALD71" s="31"/>
+      <c r="ALE71" s="31"/>
+      <c r="ALF71" s="31"/>
+      <c r="ALG71" s="31"/>
+      <c r="ALH71" s="31"/>
+      <c r="ALI71" s="31"/>
+      <c r="ALJ71" s="31"/>
+      <c r="ALK71" s="31"/>
+      <c r="ALL71" s="31"/>
+      <c r="ALM71" s="31"/>
+      <c r="ALN71" s="31"/>
+      <c r="ALO71" s="31"/>
+      <c r="ALP71" s="31"/>
+      <c r="ALQ71" s="31"/>
+      <c r="ALR71" s="31"/>
+      <c r="ALS71" s="31"/>
+      <c r="ALT71" s="31"/>
+      <c r="ALU71" s="31"/>
+      <c r="ALV71" s="31"/>
+      <c r="ALW71" s="31"/>
+      <c r="ALX71" s="31"/>
+      <c r="ALY71" s="31"/>
+      <c r="ALZ71" s="31"/>
+      <c r="AMA71" s="31"/>
+      <c r="AMB71" s="31"/>
+      <c r="AMC71" s="31"/>
+      <c r="AMD71" s="31"/>
+      <c r="AME71" s="31"/>
+      <c r="AMF71" s="31"/>
+      <c r="AMG71" s="31"/>
+      <c r="AMH71" s="31"/>
+      <c r="AMI71" s="31"/>
+      <c r="AMJ71" s="31"/>
+      <c r="AMK71" s="31"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AJ72" s="15" t="n">
@@ -15292,7 +16005,7 @@
       <c r="AG7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AK7" s="34" t="n">
+      <c r="AK7" s="32" t="n">
         <v>1</v>
       </c>
       <c r="AN7" s="4" t="n">
@@ -15307,7 +16020,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AK8" s="35" t="n">
+      <c r="AK8" s="33" t="n">
         <v>1</v>
       </c>
       <c r="AN8" s="4" t="n">
@@ -19684,12 +20397,12 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
       <c r="AN9" s="1"/>
-      <c r="AO9" s="36" t="n">
+      <c r="AO9" s="34" t="n">
         <v>2</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="1"/>
-      <c r="AR9" s="36" t="n">
+      <c r="AR9" s="34" t="n">
         <v>1</v>
       </c>
       <c r="AS9" s="1"/>

--- a/resources/mpn.xlsx
+++ b/resources/mpn.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="blank" sheetId="1" state="visible" r:id="rId3"/>
@@ -5335,9 +5335,7 @@
       <c r="F11" s="19"/>
       <c r="G11" s="18"/>
       <c r="H11" s="19"/>
-      <c r="I11" s="23" t="n">
-        <v>5</v>
-      </c>
+      <c r="I11" s="23"/>
       <c r="J11" s="18"/>
       <c r="K11" s="19"/>
       <c r="L11" s="18"/>
@@ -5349,7 +5347,9 @@
       <c r="R11" s="19"/>
       <c r="S11" s="18"/>
       <c r="T11" s="19"/>
-      <c r="U11" s="23"/>
+      <c r="U11" s="23" t="n">
+        <v>5</v>
+      </c>
       <c r="V11" s="18"/>
       <c r="W11" s="19"/>
       <c r="X11" s="18"/>
@@ -5361,7 +5361,7 @@
       <c r="AD11" s="19"/>
       <c r="AE11" s="18"/>
       <c r="AF11" s="19"/>
-      <c r="AG11" s="18"/>
+      <c r="AG11" s="23"/>
       <c r="AH11" s="18"/>
       <c r="AI11" s="19"/>
       <c r="AJ11" s="18"/>
@@ -5387,7 +5387,7 @@
       <c r="AZ11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U12" s="15" t="n">
+      <c r="AG12" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS12" s="2" t="n">
@@ -5406,7 +5406,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U14" s="15" t="n">
+      <c r="AG14" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS14" s="2" t="n">
@@ -5417,10 +5417,12 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N15" s="15" t="n">
-        <v>3</v>
-      </c>
+      <c r="N15" s="15"/>
       <c r="P15" s="16"/>
+      <c r="Z15" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB15" s="16"/>
       <c r="AP15" s="3" t="n">
         <v>1</v>
       </c>
@@ -5429,7 +5431,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U16" s="15" t="n">
+      <c r="AG16" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS16" s="2" t="n">
@@ -5448,7 +5450,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U18" s="15" t="n">
+      <c r="AG18" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS18" s="2" t="n">
@@ -5474,9 +5476,7 @@
       <c r="K19" s="19"/>
       <c r="L19" s="18"/>
       <c r="M19" s="19"/>
-      <c r="N19" s="23" t="n">
-        <v>3</v>
-      </c>
+      <c r="N19" s="23"/>
       <c r="O19" s="19"/>
       <c r="P19" s="22"/>
       <c r="Q19" s="18"/>
@@ -5488,9 +5488,11 @@
       <c r="W19" s="19"/>
       <c r="X19" s="18"/>
       <c r="Y19" s="19"/>
-      <c r="Z19" s="18"/>
+      <c r="Z19" s="23" t="n">
+        <v>3</v>
+      </c>
       <c r="AA19" s="19"/>
-      <c r="AB19" s="20"/>
+      <c r="AB19" s="22"/>
       <c r="AC19" s="18"/>
       <c r="AD19" s="19"/>
       <c r="AE19" s="18"/>
@@ -5522,8 +5524,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U20" s="15"/>
-      <c r="W20" s="15" t="n">
+      <c r="AG20" s="15"/>
+      <c r="AI20" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS20" s="2" t="n">
@@ -5531,7 +5533,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W21" s="2"/>
+      <c r="AI21" s="2"/>
       <c r="AP21" s="3" t="n">
         <v>1</v>
       </c>
@@ -5540,8 +5542,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="U22" s="15"/>
-      <c r="W22" s="15" t="n">
+      <c r="AG22" s="15"/>
+      <c r="AI22" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS22" s="2" t="n">
@@ -5549,16 +5551,17 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P23" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" s="15"/>
+      <c r="P23" s="16"/>
+      <c r="AB23" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="15"/>
       <c r="AN23" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W24" s="15" t="n">
+      <c r="AI24" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS24" s="2" t="n">
@@ -5566,7 +5569,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W25" s="15"/>
+      <c r="AI25" s="15"/>
       <c r="AY25" s="3" t="n">
         <v>5</v>
       </c>
@@ -5580,7 +5583,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W27" s="15" t="n">
+      <c r="AI27" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS27" s="2" t="n">
@@ -5610,12 +5613,10 @@
       <c r="O28" s="19"/>
       <c r="P28" s="20"/>
       <c r="Q28" s="18"/>
-      <c r="R28" s="23" t="n">
-        <v>2</v>
-      </c>
+      <c r="R28" s="23"/>
       <c r="S28" s="18"/>
       <c r="T28" s="19"/>
-      <c r="U28" s="23"/>
+      <c r="U28" s="18"/>
       <c r="V28" s="18"/>
       <c r="W28" s="19"/>
       <c r="X28" s="18"/>
@@ -5624,10 +5625,12 @@
       <c r="AA28" s="19"/>
       <c r="AB28" s="20"/>
       <c r="AC28" s="18"/>
-      <c r="AD28" s="19"/>
+      <c r="AD28" s="23" t="n">
+        <v>2</v>
+      </c>
       <c r="AE28" s="18"/>
       <c r="AF28" s="19"/>
-      <c r="AG28" s="18"/>
+      <c r="AG28" s="23"/>
       <c r="AH28" s="18"/>
       <c r="AI28" s="19"/>
       <c r="AJ28" s="18"/>
@@ -5651,7 +5654,7 @@
       <c r="AZ28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W29" s="15" t="n">
+      <c r="AI29" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS29" s="2" t="n">
@@ -5659,7 +5662,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W30" s="15"/>
+      <c r="AI30" s="15"/>
       <c r="AY30" s="3" t="n">
         <v>5</v>
       </c>
@@ -5673,7 +5676,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W32" s="15" t="n">
+      <c r="AI32" s="15" t="n">
         <v>1</v>
       </c>
       <c r="AS32" s="2" t="n">
@@ -5684,37 +5687,38 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P33" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN33" s="4" t="n">
+      <c r="P33" s="16"/>
+      <c r="AB33" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ33" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="4" t="n">
+      <c r="AI34" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" s="4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="Z35" s="2" t="n">
+      <c r="AL35" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="W36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="4" t="n">
+      <c r="AI36" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN36" s="4" t="n">
         <v>1</v>
       </c>
     </row>
